--- a/AAII_Financials/Yearly/BCH_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BCH_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
   <si>
     <t>BCH</t>
   </si>
@@ -656,111 +656,117 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>5013000</v>
+        <v>4255400</v>
       </c>
       <c r="E8" s="3">
-        <v>2692800</v>
+        <v>4702500</v>
       </c>
       <c r="F8" s="3">
-        <v>2116500</v>
+        <v>2526000</v>
       </c>
       <c r="G8" s="3">
-        <v>2386200</v>
+        <v>1985400</v>
       </c>
       <c r="H8" s="3">
-        <v>2259500</v>
+        <v>2238300</v>
       </c>
       <c r="I8" s="3">
-        <v>2126000</v>
+        <v>2119500</v>
       </c>
       <c r="J8" s="3">
+        <v>1994300</v>
+      </c>
+      <c r="K8" s="3">
         <v>2160100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2127200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2434300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2295700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2141100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2207500</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -800,9 +806,12 @@
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -842,9 +851,12 @@
       <c r="O10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -861,8 +873,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -902,9 +915,12 @@
       <c r="O12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,9 +960,12 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -986,51 +1005,57 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-95200</v>
+        <v>-97800</v>
       </c>
       <c r="E15" s="3">
-        <v>-86800</v>
+        <v>-89300</v>
       </c>
       <c r="F15" s="3">
-        <v>-82900</v>
+        <v>-81400</v>
       </c>
       <c r="G15" s="3">
-        <v>-79700</v>
+        <v>-77800</v>
       </c>
       <c r="H15" s="3">
-        <v>-42600</v>
+        <v>-74800</v>
       </c>
       <c r="I15" s="3">
-        <v>-39800</v>
+        <v>-39900</v>
       </c>
       <c r="J15" s="3">
+        <v>-37400</v>
+      </c>
+      <c r="K15" s="3">
         <v>-37600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-33100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-39000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-36000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-90000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-103300</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2783400</v>
+        <v>2633700</v>
       </c>
       <c r="E17" s="3">
-        <v>1342100</v>
+        <v>2611000</v>
       </c>
       <c r="F17" s="3">
-        <v>1124300</v>
+        <v>1259000</v>
       </c>
       <c r="G17" s="3">
-        <v>1231200</v>
+        <v>1054700</v>
       </c>
       <c r="H17" s="3">
-        <v>1086000</v>
+        <v>1154900</v>
       </c>
       <c r="I17" s="3">
-        <v>1002300</v>
+        <v>1018700</v>
       </c>
       <c r="J17" s="3">
+        <v>940200</v>
+      </c>
+      <c r="K17" s="3">
         <v>1130000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1101200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1249900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1203800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1120100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1133600</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2229600</v>
+        <v>1621700</v>
       </c>
       <c r="E18" s="3">
-        <v>1350700</v>
+        <v>2091500</v>
       </c>
       <c r="F18" s="3">
-        <v>992200</v>
+        <v>1267000</v>
       </c>
       <c r="G18" s="3">
-        <v>1155000</v>
+        <v>930700</v>
       </c>
       <c r="H18" s="3">
-        <v>1173500</v>
+        <v>1083400</v>
       </c>
       <c r="I18" s="3">
-        <v>1123700</v>
+        <v>1100800</v>
       </c>
       <c r="J18" s="3">
+        <v>1054100</v>
+      </c>
+      <c r="K18" s="3">
         <v>1030100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1026000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1184300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1091900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1021100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1073900</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,92 +1178,99 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-325300</v>
+        <v>-13100</v>
       </c>
       <c r="E20" s="3">
-        <v>-252900</v>
+        <v>-305200</v>
       </c>
       <c r="F20" s="3">
-        <v>-326500</v>
+        <v>-237200</v>
       </c>
       <c r="G20" s="3">
-        <v>-293100</v>
+        <v>-306300</v>
       </c>
       <c r="H20" s="3">
-        <v>-324400</v>
+        <v>-275000</v>
       </c>
       <c r="I20" s="3">
-        <v>-342900</v>
+        <v>-304300</v>
       </c>
       <c r="J20" s="3">
+        <v>-321600</v>
+      </c>
+      <c r="K20" s="3">
         <v>-305500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-330800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-380900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-260800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-325000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-333700</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1999400</v>
+        <v>1706400</v>
       </c>
       <c r="E21" s="3">
-        <v>1184500</v>
+        <v>1875600</v>
       </c>
       <c r="F21" s="3">
-        <v>748500</v>
+        <v>1111200</v>
       </c>
       <c r="G21" s="3">
-        <v>941600</v>
+        <v>702200</v>
       </c>
       <c r="H21" s="3">
-        <v>891700</v>
+        <v>883200</v>
       </c>
       <c r="I21" s="3">
-        <v>820700</v>
+        <v>836400</v>
       </c>
       <c r="J21" s="3">
+        <v>769900</v>
+      </c>
+      <c r="K21" s="3">
         <v>762300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>727700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>842800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>867300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>741400</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1271,93 +1310,102 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1904300</v>
+        <v>1608600</v>
       </c>
       <c r="E23" s="3">
-        <v>1097800</v>
+        <v>1786300</v>
       </c>
       <c r="F23" s="3">
-        <v>665700</v>
+        <v>1029800</v>
       </c>
       <c r="G23" s="3">
-        <v>861800</v>
+        <v>624400</v>
       </c>
       <c r="H23" s="3">
-        <v>849100</v>
+        <v>808500</v>
       </c>
       <c r="I23" s="3">
-        <v>780900</v>
+        <v>796500</v>
       </c>
       <c r="J23" s="3">
+        <v>732500</v>
+      </c>
+      <c r="K23" s="3">
         <v>724700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>695200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>803500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>831100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>696100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>740300</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>311600</v>
+        <v>290300</v>
       </c>
       <c r="E24" s="3">
-        <v>201800</v>
+        <v>292300</v>
       </c>
       <c r="F24" s="3">
-        <v>142300</v>
+        <v>189300</v>
       </c>
       <c r="G24" s="3">
-        <v>191700</v>
+        <v>133500</v>
       </c>
       <c r="H24" s="3">
-        <v>176900</v>
+        <v>179900</v>
       </c>
       <c r="I24" s="3">
-        <v>130000</v>
+        <v>165900</v>
       </c>
       <c r="J24" s="3">
+        <v>121900</v>
+      </c>
+      <c r="K24" s="3">
         <v>100600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>69100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>94800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>115800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>81800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>96200</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1592700</v>
+        <v>1318300</v>
       </c>
       <c r="E26" s="3">
-        <v>896000</v>
+        <v>1494000</v>
       </c>
       <c r="F26" s="3">
-        <v>523300</v>
+        <v>840500</v>
       </c>
       <c r="G26" s="3">
-        <v>670100</v>
+        <v>490900</v>
       </c>
       <c r="H26" s="3">
-        <v>672200</v>
+        <v>628600</v>
       </c>
       <c r="I26" s="3">
-        <v>650900</v>
+        <v>630600</v>
       </c>
       <c r="J26" s="3">
+        <v>610600</v>
+      </c>
+      <c r="K26" s="3">
         <v>624000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>626100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>708700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>715200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>614200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>644100</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1592700</v>
+        <v>1318300</v>
       </c>
       <c r="E27" s="3">
-        <v>896000</v>
+        <v>1494000</v>
       </c>
       <c r="F27" s="3">
-        <v>523300</v>
+        <v>840500</v>
       </c>
       <c r="G27" s="3">
-        <v>670100</v>
+        <v>490900</v>
       </c>
       <c r="H27" s="3">
-        <v>672200</v>
+        <v>628600</v>
       </c>
       <c r="I27" s="3">
-        <v>650900</v>
+        <v>630600</v>
       </c>
       <c r="J27" s="3">
+        <v>610600</v>
+      </c>
+      <c r="K27" s="3">
         <v>624000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>626100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>708700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>715200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>614200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>644100</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>325300</v>
+        <v>13100</v>
       </c>
       <c r="E32" s="3">
-        <v>252900</v>
+        <v>305200</v>
       </c>
       <c r="F32" s="3">
-        <v>326500</v>
+        <v>237200</v>
       </c>
       <c r="G32" s="3">
-        <v>293100</v>
+        <v>306300</v>
       </c>
       <c r="H32" s="3">
-        <v>324400</v>
+        <v>275000</v>
       </c>
       <c r="I32" s="3">
-        <v>342900</v>
+        <v>304300</v>
       </c>
       <c r="J32" s="3">
+        <v>321600</v>
+      </c>
+      <c r="K32" s="3">
         <v>305500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>330800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>380900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>260800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>325000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>333700</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1592700</v>
+        <v>1318300</v>
       </c>
       <c r="E33" s="3">
-        <v>896000</v>
+        <v>1494000</v>
       </c>
       <c r="F33" s="3">
-        <v>523300</v>
+        <v>840500</v>
       </c>
       <c r="G33" s="3">
-        <v>670100</v>
+        <v>490900</v>
       </c>
       <c r="H33" s="3">
-        <v>672200</v>
+        <v>628600</v>
       </c>
       <c r="I33" s="3">
-        <v>650900</v>
+        <v>630600</v>
       </c>
       <c r="J33" s="3">
+        <v>610600</v>
+      </c>
+      <c r="K33" s="3">
         <v>624000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>626100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>708700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>715200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>614200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>644100</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1592700</v>
+        <v>1318300</v>
       </c>
       <c r="E35" s="3">
-        <v>896000</v>
+        <v>1494000</v>
       </c>
       <c r="F35" s="3">
-        <v>523300</v>
+        <v>840500</v>
       </c>
       <c r="G35" s="3">
-        <v>670100</v>
+        <v>490900</v>
       </c>
       <c r="H35" s="3">
-        <v>672200</v>
+        <v>628600</v>
       </c>
       <c r="I35" s="3">
-        <v>650900</v>
+        <v>630600</v>
       </c>
       <c r="J35" s="3">
+        <v>610600</v>
+      </c>
+      <c r="K35" s="3">
         <v>624000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>626100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>708700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>715200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>614200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>644100</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,92 +1986,99 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>4834400</v>
+        <v>4721400</v>
       </c>
       <c r="E41" s="3">
-        <v>5339100</v>
+        <v>4534900</v>
       </c>
       <c r="F41" s="3">
-        <v>5400300</v>
+        <v>5008300</v>
       </c>
       <c r="G41" s="3">
-        <v>3155500</v>
+        <v>5065800</v>
       </c>
       <c r="H41" s="3">
-        <v>3188100</v>
+        <v>2960000</v>
       </c>
       <c r="I41" s="3">
-        <v>2222500</v>
+        <v>2990600</v>
       </c>
       <c r="J41" s="3">
+        <v>2084800</v>
+      </c>
+      <c r="K41" s="3">
         <v>2636400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3676400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2940000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2906000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1273600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1844500</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>5881900</v>
+        <v>5129400</v>
       </c>
       <c r="E42" s="3">
-        <v>9061500</v>
+        <v>5517500</v>
       </c>
       <c r="F42" s="3">
-        <v>9789200</v>
+        <v>8500200</v>
       </c>
       <c r="G42" s="3">
-        <v>6920900</v>
+        <v>9182800</v>
       </c>
       <c r="H42" s="3">
-        <v>3943700</v>
+        <v>6492200</v>
       </c>
       <c r="I42" s="3">
-        <v>3760900</v>
+        <v>3699400</v>
       </c>
       <c r="J42" s="3">
+        <v>3527900</v>
+      </c>
+      <c r="K42" s="3">
         <v>2356800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1022400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1676000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1019200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1968800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1420400</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2026,9 +2118,12 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2068,9 +2163,12 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2110,9 +2208,12 @@
       <c r="O45" s="3">
         <v>0</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2152,135 +2253,147 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>70300</v>
+        <v>81600</v>
       </c>
       <c r="E47" s="3">
-        <v>55600</v>
+        <v>65900</v>
       </c>
       <c r="F47" s="3">
-        <v>50500</v>
+        <v>52100</v>
       </c>
       <c r="G47" s="3">
-        <v>57400</v>
+        <v>47300</v>
       </c>
       <c r="H47" s="3">
-        <v>50400</v>
+        <v>53800</v>
       </c>
       <c r="I47" s="3">
-        <v>43000</v>
+        <v>47200</v>
       </c>
       <c r="J47" s="3">
+        <v>40300</v>
+      </c>
+      <c r="K47" s="3">
         <v>36800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>31500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>30100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>18700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>14900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>19400</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>358400</v>
+        <v>341600</v>
       </c>
       <c r="E48" s="3">
-        <v>378500</v>
+        <v>336200</v>
       </c>
       <c r="F48" s="3">
-        <v>395000</v>
+        <v>355100</v>
       </c>
       <c r="G48" s="3">
-        <v>434100</v>
+        <v>370600</v>
       </c>
       <c r="H48" s="3">
-        <v>259700</v>
+        <v>407200</v>
       </c>
       <c r="I48" s="3">
-        <v>260500</v>
+        <v>243600</v>
       </c>
       <c r="J48" s="3">
+        <v>244400</v>
+      </c>
+      <c r="K48" s="3">
         <v>264100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>258400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>836300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>278100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>284000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>330700</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>120500</v>
+        <v>145400</v>
       </c>
       <c r="E49" s="3">
-        <v>82000</v>
+        <v>113000</v>
       </c>
       <c r="F49" s="3">
-        <v>68600</v>
+        <v>76900</v>
       </c>
       <c r="G49" s="3">
-        <v>65900</v>
+        <v>64300</v>
       </c>
       <c r="H49" s="3">
-        <v>58800</v>
+        <v>61800</v>
       </c>
       <c r="I49" s="3">
-        <v>44100</v>
+        <v>55200</v>
       </c>
       <c r="J49" s="3">
+        <v>41400</v>
+      </c>
+      <c r="K49" s="3">
         <v>33200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>29900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>59700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>93900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>96800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>119100</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>621900</v>
+        <v>596500</v>
       </c>
       <c r="E52" s="3">
-        <v>496300</v>
+        <v>583400</v>
       </c>
       <c r="F52" s="3">
-        <v>404500</v>
+        <v>465500</v>
       </c>
       <c r="G52" s="3">
-        <v>362700</v>
+        <v>379400</v>
       </c>
       <c r="H52" s="3">
-        <v>314100</v>
+        <v>340200</v>
       </c>
       <c r="I52" s="3">
-        <v>302200</v>
+        <v>294600</v>
       </c>
       <c r="J52" s="3">
+        <v>283400</v>
+      </c>
+      <c r="K52" s="3">
         <v>318300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>286700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>241400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>73300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>71400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>88200</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>62438600</v>
+        <v>59140100</v>
       </c>
       <c r="E54" s="3">
-        <v>58423800</v>
+        <v>58570700</v>
       </c>
       <c r="F54" s="3">
-        <v>52087500</v>
+        <v>54804600</v>
       </c>
       <c r="G54" s="3">
-        <v>46638900</v>
+        <v>48860800</v>
       </c>
       <c r="H54" s="3">
-        <v>40596900</v>
+        <v>43749700</v>
       </c>
       <c r="I54" s="3">
-        <v>37091300</v>
+        <v>38082000</v>
       </c>
       <c r="J54" s="3">
+        <v>34793600</v>
+      </c>
+      <c r="K54" s="3">
         <v>35633100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>35048100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>32898500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>33635800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>29693700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>31981300</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,134 +2654,144 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1353200</v>
+        <v>741100</v>
       </c>
       <c r="E57" s="3">
-        <v>769400</v>
+        <v>1269400</v>
       </c>
       <c r="F57" s="3">
-        <v>1779900</v>
+        <v>721800</v>
       </c>
       <c r="G57" s="3">
-        <v>659500</v>
+        <v>1669700</v>
       </c>
       <c r="H57" s="3">
-        <v>579000</v>
+        <v>618600</v>
       </c>
       <c r="I57" s="3">
-        <v>549000</v>
+        <v>543100</v>
       </c>
       <c r="J57" s="3">
+        <v>515000</v>
+      </c>
+      <c r="K57" s="3">
         <v>385800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>406900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>259800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>197600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>93000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>228500</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3635000</v>
+        <v>3013600</v>
       </c>
       <c r="E58" s="3">
-        <v>3789600</v>
+        <v>3409800</v>
       </c>
       <c r="F58" s="3">
-        <v>2727500</v>
+        <v>3554800</v>
       </c>
       <c r="G58" s="3">
-        <v>3536400</v>
+        <v>2558500</v>
       </c>
       <c r="H58" s="3">
-        <v>3498100</v>
+        <v>3317300</v>
       </c>
       <c r="I58" s="3">
-        <v>2839200</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>5</v>
+        <v>3281400</v>
+      </c>
+      <c r="J58" s="3">
+        <v>2663400</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L58" s="3">
+      <c r="L58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M58" s="3">
         <v>1366100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1272200</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>603200</v>
+        <v>672200</v>
       </c>
       <c r="E59" s="3">
-        <v>499600</v>
+        <v>565900</v>
       </c>
       <c r="F59" s="3">
-        <v>254100</v>
+        <v>468700</v>
       </c>
       <c r="G59" s="3">
-        <v>427400</v>
+        <v>238400</v>
       </c>
       <c r="H59" s="3">
-        <v>370000</v>
+        <v>400900</v>
       </c>
       <c r="I59" s="3">
-        <v>358800</v>
+        <v>347100</v>
       </c>
       <c r="J59" s="3">
+        <v>336600</v>
+      </c>
+      <c r="K59" s="3">
         <v>323900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>32800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>125000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>97600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>29700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4500</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2692,93 +2831,102 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>14813600</v>
+        <v>14326400</v>
       </c>
       <c r="E61" s="3">
-        <v>12941300</v>
+        <v>13895900</v>
       </c>
       <c r="F61" s="3">
-        <v>11803200</v>
+        <v>12139600</v>
       </c>
       <c r="G61" s="3">
-        <v>8879700</v>
+        <v>11072000</v>
       </c>
       <c r="H61" s="3">
-        <v>7139900</v>
+        <v>8329600</v>
       </c>
       <c r="I61" s="3">
-        <v>6219500</v>
+        <v>6697600</v>
       </c>
       <c r="J61" s="3">
+        <v>5834200</v>
+      </c>
+      <c r="K61" s="3">
         <v>8366700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8741500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7548500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6299100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6304100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6900100</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1064200</v>
+        <v>1019000</v>
       </c>
       <c r="E62" s="3">
-        <v>818300</v>
+        <v>998300</v>
       </c>
       <c r="F62" s="3">
-        <v>580400</v>
+        <v>767600</v>
       </c>
       <c r="G62" s="3">
-        <v>434100</v>
+        <v>544500</v>
       </c>
       <c r="H62" s="3">
-        <v>412100</v>
+        <v>407300</v>
       </c>
       <c r="I62" s="3">
-        <v>432700</v>
+        <v>386600</v>
       </c>
       <c r="J62" s="3">
+        <v>405900</v>
+      </c>
+      <c r="K62" s="3">
         <v>425800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>752600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>757700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>201000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>82600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>89100</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>56948700</v>
+        <v>53588600</v>
       </c>
       <c r="E66" s="3">
-        <v>53651800</v>
+        <v>53420900</v>
       </c>
       <c r="F66" s="3">
-        <v>47876800</v>
+        <v>50328200</v>
       </c>
       <c r="G66" s="3">
-        <v>42652000</v>
+        <v>44911000</v>
       </c>
       <c r="H66" s="3">
-        <v>36863200</v>
+        <v>40009800</v>
       </c>
       <c r="I66" s="3">
-        <v>33581900</v>
+        <v>34579600</v>
       </c>
       <c r="J66" s="3">
+        <v>31501600</v>
+      </c>
+      <c r="K66" s="3">
         <v>32370300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>31979200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>29881700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>30153100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>26678700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>28981500</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2868000</v>
+        <v>2956400</v>
       </c>
       <c r="E72" s="3">
-        <v>2035800</v>
+        <v>2690300</v>
       </c>
       <c r="F72" s="3">
-        <v>1556400</v>
+        <v>1909700</v>
       </c>
       <c r="G72" s="3">
-        <v>1340900</v>
+        <v>1460000</v>
       </c>
       <c r="H72" s="3">
-        <v>1060800</v>
+        <v>1257800</v>
       </c>
       <c r="I72" s="3">
-        <v>954900</v>
+        <v>995100</v>
       </c>
       <c r="J72" s="3">
+        <v>895700</v>
+      </c>
+      <c r="K72" s="3">
         <v>876900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>718100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>649900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1048700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1075700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1077500</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>5489900</v>
+        <v>5551500</v>
       </c>
       <c r="E76" s="3">
-        <v>4772000</v>
+        <v>5149800</v>
       </c>
       <c r="F76" s="3">
-        <v>4210700</v>
+        <v>4476400</v>
       </c>
       <c r="G76" s="3">
-        <v>3986900</v>
+        <v>3949800</v>
       </c>
       <c r="H76" s="3">
-        <v>3733700</v>
+        <v>3739900</v>
       </c>
       <c r="I76" s="3">
-        <v>3509500</v>
+        <v>3502400</v>
       </c>
       <c r="J76" s="3">
+        <v>3292100</v>
+      </c>
+      <c r="K76" s="3">
         <v>3262800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3068900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3016800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3482700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3015000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2999800</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1592700</v>
+        <v>1318300</v>
       </c>
       <c r="E81" s="3">
-        <v>896000</v>
+        <v>1494000</v>
       </c>
       <c r="F81" s="3">
-        <v>523300</v>
+        <v>840500</v>
       </c>
       <c r="G81" s="3">
-        <v>670100</v>
+        <v>490900</v>
       </c>
       <c r="H81" s="3">
-        <v>672200</v>
+        <v>628600</v>
       </c>
       <c r="I81" s="3">
-        <v>650900</v>
+        <v>630600</v>
       </c>
       <c r="J81" s="3">
+        <v>610600</v>
+      </c>
+      <c r="K81" s="3">
         <v>624000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>626100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>708700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>715200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>614200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>644100</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>95200</v>
+        <v>97800</v>
       </c>
       <c r="E83" s="3">
-        <v>86800</v>
+        <v>89300</v>
       </c>
       <c r="F83" s="3">
-        <v>82900</v>
+        <v>81400</v>
       </c>
       <c r="G83" s="3">
-        <v>79700</v>
+        <v>77800</v>
       </c>
       <c r="H83" s="3">
-        <v>42600</v>
+        <v>74800</v>
       </c>
       <c r="I83" s="3">
-        <v>39800</v>
+        <v>39900</v>
       </c>
       <c r="J83" s="3">
+        <v>37400</v>
+      </c>
+      <c r="K83" s="3">
         <v>37600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>33100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>39000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>36000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>45000</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-376900</v>
+        <v>1103900</v>
       </c>
       <c r="E89" s="3">
-        <v>2745300</v>
+        <v>-353600</v>
       </c>
       <c r="F89" s="3">
-        <v>587200</v>
+        <v>2575300</v>
       </c>
       <c r="G89" s="3">
-        <v>1396500</v>
+        <v>550800</v>
       </c>
       <c r="H89" s="3">
-        <v>-1130600</v>
+        <v>1310000</v>
       </c>
       <c r="I89" s="3">
-        <v>1206300</v>
+        <v>-1060600</v>
       </c>
       <c r="J89" s="3">
+        <v>1131500</v>
+      </c>
+      <c r="K89" s="3">
         <v>384600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1594600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-273200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-181800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-532500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-668700</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-24000</v>
+        <v>-28300</v>
       </c>
       <c r="E91" s="3">
-        <v>-40200</v>
+        <v>-22500</v>
       </c>
       <c r="F91" s="3">
-        <v>-33100</v>
+        <v>-37700</v>
       </c>
       <c r="G91" s="3">
-        <v>-49200</v>
+        <v>-31100</v>
       </c>
       <c r="H91" s="3">
-        <v>-31700</v>
+        <v>-46100</v>
       </c>
       <c r="I91" s="3">
-        <v>-26200</v>
+        <v>-29700</v>
       </c>
       <c r="J91" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="K91" s="3">
         <v>-31400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-35300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-37500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-15900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-23000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-32400</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-82100</v>
+        <v>-82000</v>
       </c>
       <c r="E94" s="3">
-        <v>-3277400</v>
+        <v>-77000</v>
       </c>
       <c r="F94" s="3">
-        <v>237200</v>
+        <v>-3074300</v>
       </c>
       <c r="G94" s="3">
-        <v>-449300</v>
+        <v>222500</v>
       </c>
       <c r="H94" s="3">
-        <v>470600</v>
+        <v>-421400</v>
       </c>
       <c r="I94" s="3">
-        <v>-1332700</v>
+        <v>441400</v>
       </c>
       <c r="J94" s="3">
+        <v>-1250100</v>
+      </c>
+      <c r="K94" s="3">
         <v>455600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>448100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>58600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-532000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>246200</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-610000</v>
+        <v>-918900</v>
       </c>
       <c r="E96" s="3">
-        <v>-248900</v>
+        <v>-572200</v>
       </c>
       <c r="F96" s="3">
-        <v>-396100</v>
+        <v>-233500</v>
       </c>
       <c r="G96" s="3">
-        <v>-402600</v>
+        <v>-371600</v>
       </c>
       <c r="H96" s="3">
-        <v>-422700</v>
+        <v>-377700</v>
       </c>
       <c r="I96" s="3">
-        <v>-386500</v>
+        <v>-396500</v>
       </c>
       <c r="J96" s="3">
+        <v>-362600</v>
+      </c>
+      <c r="K96" s="3">
         <v>-414300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-411500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-438100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-446500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-379900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-410400</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-921200</v>
+        <v>-1633400</v>
       </c>
       <c r="E100" s="3">
-        <v>1520800</v>
+        <v>-864100</v>
       </c>
       <c r="F100" s="3">
-        <v>1651600</v>
+        <v>1426600</v>
       </c>
       <c r="G100" s="3">
-        <v>906800</v>
+        <v>1549300</v>
       </c>
       <c r="H100" s="3">
-        <v>728800</v>
+        <v>850600</v>
       </c>
       <c r="I100" s="3">
-        <v>149900</v>
+        <v>683700</v>
       </c>
       <c r="J100" s="3">
+        <v>140600</v>
+      </c>
+      <c r="K100" s="3">
         <v>-804100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1359500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>449300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1002100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>61600</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>43000</v>
+        <v>16600</v>
       </c>
       <c r="E101" s="3">
-        <v>367200</v>
+        <v>40300</v>
       </c>
       <c r="F101" s="3">
-        <v>-38800</v>
+        <v>344500</v>
       </c>
       <c r="G101" s="3">
-        <v>38800</v>
+        <v>-36400</v>
       </c>
       <c r="H101" s="3">
-        <v>131200</v>
+        <v>36400</v>
       </c>
       <c r="I101" s="3">
-        <v>-43400</v>
+        <v>123100</v>
       </c>
       <c r="J101" s="3">
+        <v>-40700</v>
+      </c>
+      <c r="K101" s="3">
         <v>-32600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>87500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>55000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>78600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-40600</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-1337300</v>
+        <v>-594900</v>
       </c>
       <c r="E102" s="3">
-        <v>1356000</v>
+        <v>-1254400</v>
       </c>
       <c r="F102" s="3">
-        <v>2437100</v>
+        <v>1272000</v>
       </c>
       <c r="G102" s="3">
-        <v>1892700</v>
+        <v>2286100</v>
       </c>
       <c r="H102" s="3">
-        <v>200000</v>
+        <v>1775500</v>
       </c>
       <c r="I102" s="3">
-        <v>-19900</v>
+        <v>187600</v>
       </c>
       <c r="J102" s="3">
+        <v>-18600</v>
+      </c>
+      <c r="K102" s="3">
         <v>3500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>300500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>289700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>366900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-265300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>190700</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/BCH_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BCH_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>4255400</v>
+        <v>4375800</v>
       </c>
       <c r="E8" s="3">
-        <v>4702500</v>
+        <v>4835600</v>
       </c>
       <c r="F8" s="3">
-        <v>2526000</v>
+        <v>2597500</v>
       </c>
       <c r="G8" s="3">
-        <v>1985400</v>
+        <v>2041600</v>
       </c>
       <c r="H8" s="3">
-        <v>2238300</v>
+        <v>2301700</v>
       </c>
       <c r="I8" s="3">
-        <v>2119500</v>
+        <v>2179500</v>
       </c>
       <c r="J8" s="3">
-        <v>1994300</v>
+        <v>2050800</v>
       </c>
       <c r="K8" s="3">
         <v>2160100</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-97800</v>
+        <v>-100600</v>
       </c>
       <c r="E15" s="3">
-        <v>-89300</v>
+        <v>-91800</v>
       </c>
       <c r="F15" s="3">
-        <v>-81400</v>
+        <v>-83700</v>
       </c>
       <c r="G15" s="3">
-        <v>-77800</v>
+        <v>-80000</v>
       </c>
       <c r="H15" s="3">
-        <v>-74800</v>
+        <v>-76900</v>
       </c>
       <c r="I15" s="3">
-        <v>-39900</v>
+        <v>-41100</v>
       </c>
       <c r="J15" s="3">
-        <v>-37400</v>
+        <v>-38400</v>
       </c>
       <c r="K15" s="3">
         <v>-37600</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2633700</v>
+        <v>2708200</v>
       </c>
       <c r="E17" s="3">
-        <v>2611000</v>
+        <v>2684900</v>
       </c>
       <c r="F17" s="3">
-        <v>1259000</v>
+        <v>1294600</v>
       </c>
       <c r="G17" s="3">
-        <v>1054700</v>
+        <v>1084500</v>
       </c>
       <c r="H17" s="3">
-        <v>1154900</v>
+        <v>1187600</v>
       </c>
       <c r="I17" s="3">
-        <v>1018700</v>
+        <v>1047500</v>
       </c>
       <c r="J17" s="3">
-        <v>940200</v>
+        <v>966800</v>
       </c>
       <c r="K17" s="3">
         <v>1130000</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1621700</v>
+        <v>1667600</v>
       </c>
       <c r="E18" s="3">
-        <v>2091500</v>
+        <v>2150700</v>
       </c>
       <c r="F18" s="3">
-        <v>1267000</v>
+        <v>1302900</v>
       </c>
       <c r="G18" s="3">
-        <v>930700</v>
+        <v>957100</v>
       </c>
       <c r="H18" s="3">
-        <v>1083400</v>
+        <v>1114100</v>
       </c>
       <c r="I18" s="3">
-        <v>1100800</v>
+        <v>1132000</v>
       </c>
       <c r="J18" s="3">
-        <v>1054100</v>
+        <v>1084000</v>
       </c>
       <c r="K18" s="3">
         <v>1030100</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-13100</v>
+        <v>-13500</v>
       </c>
       <c r="E20" s="3">
-        <v>-305200</v>
+        <v>-313800</v>
       </c>
       <c r="F20" s="3">
-        <v>-237200</v>
+        <v>-244000</v>
       </c>
       <c r="G20" s="3">
-        <v>-306300</v>
+        <v>-315000</v>
       </c>
       <c r="H20" s="3">
-        <v>-275000</v>
+        <v>-282800</v>
       </c>
       <c r="I20" s="3">
-        <v>-304300</v>
+        <v>-312900</v>
       </c>
       <c r="J20" s="3">
-        <v>-321600</v>
+        <v>-330700</v>
       </c>
       <c r="K20" s="3">
         <v>-305500</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1706400</v>
+        <v>1753800</v>
       </c>
       <c r="E21" s="3">
-        <v>1875600</v>
+        <v>1927800</v>
       </c>
       <c r="F21" s="3">
-        <v>1111200</v>
+        <v>1141800</v>
       </c>
       <c r="G21" s="3">
-        <v>702200</v>
+        <v>721300</v>
       </c>
       <c r="H21" s="3">
-        <v>883200</v>
+        <v>907500</v>
       </c>
       <c r="I21" s="3">
-        <v>836400</v>
+        <v>859700</v>
       </c>
       <c r="J21" s="3">
-        <v>769900</v>
+        <v>791300</v>
       </c>
       <c r="K21" s="3">
         <v>762300</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1608600</v>
+        <v>1654100</v>
       </c>
       <c r="E23" s="3">
-        <v>1786300</v>
+        <v>1836900</v>
       </c>
       <c r="F23" s="3">
-        <v>1029800</v>
+        <v>1058900</v>
       </c>
       <c r="G23" s="3">
-        <v>624400</v>
+        <v>642100</v>
       </c>
       <c r="H23" s="3">
-        <v>808500</v>
+        <v>831300</v>
       </c>
       <c r="I23" s="3">
-        <v>796500</v>
+        <v>819000</v>
       </c>
       <c r="J23" s="3">
-        <v>732500</v>
+        <v>753200</v>
       </c>
       <c r="K23" s="3">
         <v>724700</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>290300</v>
+        <v>298500</v>
       </c>
       <c r="E24" s="3">
-        <v>292300</v>
+        <v>300600</v>
       </c>
       <c r="F24" s="3">
-        <v>189300</v>
+        <v>194600</v>
       </c>
       <c r="G24" s="3">
-        <v>133500</v>
+        <v>137300</v>
       </c>
       <c r="H24" s="3">
-        <v>179900</v>
+        <v>185000</v>
       </c>
       <c r="I24" s="3">
-        <v>165900</v>
+        <v>170600</v>
       </c>
       <c r="J24" s="3">
-        <v>121900</v>
+        <v>125400</v>
       </c>
       <c r="K24" s="3">
         <v>100600</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1318300</v>
+        <v>1355600</v>
       </c>
       <c r="E26" s="3">
-        <v>1494000</v>
+        <v>1536300</v>
       </c>
       <c r="F26" s="3">
-        <v>840500</v>
+        <v>864300</v>
       </c>
       <c r="G26" s="3">
-        <v>490900</v>
+        <v>504800</v>
       </c>
       <c r="H26" s="3">
-        <v>628600</v>
+        <v>646400</v>
       </c>
       <c r="I26" s="3">
-        <v>630600</v>
+        <v>648400</v>
       </c>
       <c r="J26" s="3">
-        <v>610600</v>
+        <v>627900</v>
       </c>
       <c r="K26" s="3">
         <v>624000</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1318300</v>
+        <v>1355600</v>
       </c>
       <c r="E27" s="3">
-        <v>1494000</v>
+        <v>1536300</v>
       </c>
       <c r="F27" s="3">
-        <v>840500</v>
+        <v>864300</v>
       </c>
       <c r="G27" s="3">
-        <v>490900</v>
+        <v>504800</v>
       </c>
       <c r="H27" s="3">
-        <v>628600</v>
+        <v>646400</v>
       </c>
       <c r="I27" s="3">
-        <v>630600</v>
+        <v>648400</v>
       </c>
       <c r="J27" s="3">
-        <v>610600</v>
+        <v>627900</v>
       </c>
       <c r="K27" s="3">
         <v>624000</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>13100</v>
+        <v>13500</v>
       </c>
       <c r="E32" s="3">
-        <v>305200</v>
+        <v>313800</v>
       </c>
       <c r="F32" s="3">
-        <v>237200</v>
+        <v>244000</v>
       </c>
       <c r="G32" s="3">
-        <v>306300</v>
+        <v>315000</v>
       </c>
       <c r="H32" s="3">
-        <v>275000</v>
+        <v>282800</v>
       </c>
       <c r="I32" s="3">
-        <v>304300</v>
+        <v>312900</v>
       </c>
       <c r="J32" s="3">
-        <v>321600</v>
+        <v>330700</v>
       </c>
       <c r="K32" s="3">
         <v>305500</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1318300</v>
+        <v>1355600</v>
       </c>
       <c r="E33" s="3">
-        <v>1494000</v>
+        <v>1536300</v>
       </c>
       <c r="F33" s="3">
-        <v>840500</v>
+        <v>864300</v>
       </c>
       <c r="G33" s="3">
-        <v>490900</v>
+        <v>504800</v>
       </c>
       <c r="H33" s="3">
-        <v>628600</v>
+        <v>646400</v>
       </c>
       <c r="I33" s="3">
-        <v>630600</v>
+        <v>648400</v>
       </c>
       <c r="J33" s="3">
-        <v>610600</v>
+        <v>627900</v>
       </c>
       <c r="K33" s="3">
         <v>624000</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1318300</v>
+        <v>1355600</v>
       </c>
       <c r="E35" s="3">
-        <v>1494000</v>
+        <v>1536300</v>
       </c>
       <c r="F35" s="3">
-        <v>840500</v>
+        <v>864300</v>
       </c>
       <c r="G35" s="3">
-        <v>490900</v>
+        <v>504800</v>
       </c>
       <c r="H35" s="3">
-        <v>628600</v>
+        <v>646400</v>
       </c>
       <c r="I35" s="3">
-        <v>630600</v>
+        <v>648400</v>
       </c>
       <c r="J35" s="3">
-        <v>610600</v>
+        <v>627900</v>
       </c>
       <c r="K35" s="3">
         <v>624000</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>4721400</v>
+        <v>4855000</v>
       </c>
       <c r="E41" s="3">
-        <v>4534900</v>
+        <v>4663200</v>
       </c>
       <c r="F41" s="3">
-        <v>5008300</v>
+        <v>5150100</v>
       </c>
       <c r="G41" s="3">
-        <v>5065800</v>
+        <v>5209100</v>
       </c>
       <c r="H41" s="3">
-        <v>2960000</v>
+        <v>3043800</v>
       </c>
       <c r="I41" s="3">
-        <v>2990600</v>
+        <v>3075200</v>
       </c>
       <c r="J41" s="3">
-        <v>2084800</v>
+        <v>2143800</v>
       </c>
       <c r="K41" s="3">
         <v>2636400</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>5129400</v>
+        <v>5274500</v>
       </c>
       <c r="E42" s="3">
-        <v>5517500</v>
+        <v>5673700</v>
       </c>
       <c r="F42" s="3">
-        <v>8500200</v>
+        <v>8740700</v>
       </c>
       <c r="G42" s="3">
-        <v>9182800</v>
+        <v>9442700</v>
       </c>
       <c r="H42" s="3">
-        <v>6492200</v>
+        <v>6676000</v>
       </c>
       <c r="I42" s="3">
-        <v>3699400</v>
+        <v>3804100</v>
       </c>
       <c r="J42" s="3">
-        <v>3527900</v>
+        <v>3627800</v>
       </c>
       <c r="K42" s="3">
         <v>2356800</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>81600</v>
+        <v>83900</v>
       </c>
       <c r="E47" s="3">
-        <v>65900</v>
+        <v>67800</v>
       </c>
       <c r="F47" s="3">
-        <v>52100</v>
+        <v>53600</v>
       </c>
       <c r="G47" s="3">
-        <v>47300</v>
+        <v>48700</v>
       </c>
       <c r="H47" s="3">
-        <v>53800</v>
+        <v>55300</v>
       </c>
       <c r="I47" s="3">
-        <v>47200</v>
+        <v>48600</v>
       </c>
       <c r="J47" s="3">
-        <v>40300</v>
+        <v>41500</v>
       </c>
       <c r="K47" s="3">
         <v>36800</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>341600</v>
+        <v>351300</v>
       </c>
       <c r="E48" s="3">
-        <v>336200</v>
+        <v>345700</v>
       </c>
       <c r="F48" s="3">
-        <v>355100</v>
+        <v>365100</v>
       </c>
       <c r="G48" s="3">
-        <v>370600</v>
+        <v>381100</v>
       </c>
       <c r="H48" s="3">
-        <v>407200</v>
+        <v>418700</v>
       </c>
       <c r="I48" s="3">
-        <v>243600</v>
+        <v>250500</v>
       </c>
       <c r="J48" s="3">
-        <v>244400</v>
+        <v>251300</v>
       </c>
       <c r="K48" s="3">
         <v>264100</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>145400</v>
+        <v>149600</v>
       </c>
       <c r="E49" s="3">
-        <v>113000</v>
+        <v>116200</v>
       </c>
       <c r="F49" s="3">
-        <v>76900</v>
+        <v>79100</v>
       </c>
       <c r="G49" s="3">
-        <v>64300</v>
+        <v>66200</v>
       </c>
       <c r="H49" s="3">
-        <v>61800</v>
+        <v>63600</v>
       </c>
       <c r="I49" s="3">
-        <v>55200</v>
+        <v>56700</v>
       </c>
       <c r="J49" s="3">
-        <v>41400</v>
+        <v>42600</v>
       </c>
       <c r="K49" s="3">
         <v>33200</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>596500</v>
+        <v>613400</v>
       </c>
       <c r="E52" s="3">
-        <v>583400</v>
+        <v>599900</v>
       </c>
       <c r="F52" s="3">
-        <v>465500</v>
+        <v>478700</v>
       </c>
       <c r="G52" s="3">
-        <v>379400</v>
+        <v>390200</v>
       </c>
       <c r="H52" s="3">
-        <v>340200</v>
+        <v>349800</v>
       </c>
       <c r="I52" s="3">
-        <v>294600</v>
+        <v>302900</v>
       </c>
       <c r="J52" s="3">
-        <v>283400</v>
+        <v>291500</v>
       </c>
       <c r="K52" s="3">
         <v>318300</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>59140100</v>
+        <v>60813900</v>
       </c>
       <c r="E54" s="3">
-        <v>58570700</v>
+        <v>60228300</v>
       </c>
       <c r="F54" s="3">
-        <v>54804600</v>
+        <v>56355700</v>
       </c>
       <c r="G54" s="3">
-        <v>48860800</v>
+        <v>50243700</v>
       </c>
       <c r="H54" s="3">
-        <v>43749700</v>
+        <v>44987900</v>
       </c>
       <c r="I54" s="3">
-        <v>38082000</v>
+        <v>39159800</v>
       </c>
       <c r="J54" s="3">
-        <v>34793600</v>
+        <v>35778400</v>
       </c>
       <c r="K54" s="3">
         <v>35633100</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>741100</v>
+        <v>762100</v>
       </c>
       <c r="E57" s="3">
-        <v>1269400</v>
+        <v>1305300</v>
       </c>
       <c r="F57" s="3">
-        <v>721800</v>
+        <v>742200</v>
       </c>
       <c r="G57" s="3">
-        <v>1669700</v>
+        <v>1716900</v>
       </c>
       <c r="H57" s="3">
-        <v>618600</v>
+        <v>636100</v>
       </c>
       <c r="I57" s="3">
-        <v>543100</v>
+        <v>558500</v>
       </c>
       <c r="J57" s="3">
-        <v>515000</v>
+        <v>529600</v>
       </c>
       <c r="K57" s="3">
         <v>385800</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3013600</v>
+        <v>3098900</v>
       </c>
       <c r="E58" s="3">
-        <v>3409800</v>
+        <v>3506300</v>
       </c>
       <c r="F58" s="3">
-        <v>3554800</v>
+        <v>3655400</v>
       </c>
       <c r="G58" s="3">
-        <v>2558500</v>
+        <v>2630900</v>
       </c>
       <c r="H58" s="3">
-        <v>3317300</v>
+        <v>3411200</v>
       </c>
       <c r="I58" s="3">
-        <v>3281400</v>
+        <v>3374300</v>
       </c>
       <c r="J58" s="3">
-        <v>2663400</v>
+        <v>2738700</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>5</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>672200</v>
+        <v>691200</v>
       </c>
       <c r="E59" s="3">
-        <v>565900</v>
+        <v>581900</v>
       </c>
       <c r="F59" s="3">
-        <v>468700</v>
+        <v>482000</v>
       </c>
       <c r="G59" s="3">
-        <v>238400</v>
+        <v>245100</v>
       </c>
       <c r="H59" s="3">
-        <v>400900</v>
+        <v>412200</v>
       </c>
       <c r="I59" s="3">
-        <v>347100</v>
+        <v>356900</v>
       </c>
       <c r="J59" s="3">
-        <v>336600</v>
+        <v>346100</v>
       </c>
       <c r="K59" s="3">
         <v>323900</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>14326400</v>
+        <v>14731900</v>
       </c>
       <c r="E61" s="3">
-        <v>13895900</v>
+        <v>14289200</v>
       </c>
       <c r="F61" s="3">
-        <v>12139600</v>
+        <v>12483200</v>
       </c>
       <c r="G61" s="3">
-        <v>11072000</v>
+        <v>11385400</v>
       </c>
       <c r="H61" s="3">
-        <v>8329600</v>
+        <v>8565400</v>
       </c>
       <c r="I61" s="3">
-        <v>6697600</v>
+        <v>6887100</v>
       </c>
       <c r="J61" s="3">
-        <v>5834200</v>
+        <v>5999300</v>
       </c>
       <c r="K61" s="3">
         <v>8366700</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1019000</v>
+        <v>1047800</v>
       </c>
       <c r="E62" s="3">
-        <v>998300</v>
+        <v>1026600</v>
       </c>
       <c r="F62" s="3">
-        <v>767600</v>
+        <v>789300</v>
       </c>
       <c r="G62" s="3">
-        <v>544500</v>
+        <v>559900</v>
       </c>
       <c r="H62" s="3">
-        <v>407300</v>
+        <v>418800</v>
       </c>
       <c r="I62" s="3">
-        <v>386600</v>
+        <v>397500</v>
       </c>
       <c r="J62" s="3">
-        <v>405900</v>
+        <v>417400</v>
       </c>
       <c r="K62" s="3">
         <v>425800</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>53588600</v>
+        <v>55105200</v>
       </c>
       <c r="E66" s="3">
-        <v>53420900</v>
+        <v>54932800</v>
       </c>
       <c r="F66" s="3">
-        <v>50328200</v>
+        <v>51752600</v>
       </c>
       <c r="G66" s="3">
-        <v>44911000</v>
+        <v>46182100</v>
       </c>
       <c r="H66" s="3">
-        <v>40009800</v>
+        <v>41142200</v>
       </c>
       <c r="I66" s="3">
-        <v>34579600</v>
+        <v>35558300</v>
       </c>
       <c r="J66" s="3">
-        <v>31501600</v>
+        <v>32393100</v>
       </c>
       <c r="K66" s="3">
         <v>32370300</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2956400</v>
+        <v>3040000</v>
       </c>
       <c r="E72" s="3">
-        <v>2690300</v>
+        <v>2766500</v>
       </c>
       <c r="F72" s="3">
-        <v>1909700</v>
+        <v>1963800</v>
       </c>
       <c r="G72" s="3">
-        <v>1460000</v>
+        <v>1501300</v>
       </c>
       <c r="H72" s="3">
-        <v>1257800</v>
+        <v>1293400</v>
       </c>
       <c r="I72" s="3">
-        <v>995100</v>
+        <v>1023200</v>
       </c>
       <c r="J72" s="3">
-        <v>895700</v>
+        <v>921100</v>
       </c>
       <c r="K72" s="3">
         <v>876900</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>5551500</v>
+        <v>5708600</v>
       </c>
       <c r="E76" s="3">
-        <v>5149800</v>
+        <v>5295600</v>
       </c>
       <c r="F76" s="3">
-        <v>4476400</v>
+        <v>4603100</v>
       </c>
       <c r="G76" s="3">
-        <v>3949800</v>
+        <v>4061600</v>
       </c>
       <c r="H76" s="3">
-        <v>3739900</v>
+        <v>3845800</v>
       </c>
       <c r="I76" s="3">
-        <v>3502400</v>
+        <v>3601500</v>
       </c>
       <c r="J76" s="3">
-        <v>3292100</v>
+        <v>3385200</v>
       </c>
       <c r="K76" s="3">
         <v>3262800</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1318300</v>
+        <v>1355600</v>
       </c>
       <c r="E81" s="3">
-        <v>1494000</v>
+        <v>1536300</v>
       </c>
       <c r="F81" s="3">
-        <v>840500</v>
+        <v>864300</v>
       </c>
       <c r="G81" s="3">
-        <v>490900</v>
+        <v>504800</v>
       </c>
       <c r="H81" s="3">
-        <v>628600</v>
+        <v>646400</v>
       </c>
       <c r="I81" s="3">
-        <v>630600</v>
+        <v>648400</v>
       </c>
       <c r="J81" s="3">
-        <v>610600</v>
+        <v>627900</v>
       </c>
       <c r="K81" s="3">
         <v>624000</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>97800</v>
+        <v>100600</v>
       </c>
       <c r="E83" s="3">
-        <v>89300</v>
+        <v>91800</v>
       </c>
       <c r="F83" s="3">
-        <v>81400</v>
+        <v>83700</v>
       </c>
       <c r="G83" s="3">
-        <v>77800</v>
+        <v>80000</v>
       </c>
       <c r="H83" s="3">
-        <v>74800</v>
+        <v>76900</v>
       </c>
       <c r="I83" s="3">
-        <v>39900</v>
+        <v>41100</v>
       </c>
       <c r="J83" s="3">
-        <v>37400</v>
+        <v>38400</v>
       </c>
       <c r="K83" s="3">
         <v>37600</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1103900</v>
+        <v>1135100</v>
       </c>
       <c r="E89" s="3">
-        <v>-353600</v>
+        <v>-363600</v>
       </c>
       <c r="F89" s="3">
-        <v>2575300</v>
+        <v>2648100</v>
       </c>
       <c r="G89" s="3">
-        <v>550800</v>
+        <v>566400</v>
       </c>
       <c r="H89" s="3">
-        <v>1310000</v>
+        <v>1347100</v>
       </c>
       <c r="I89" s="3">
-        <v>-1060600</v>
+        <v>-1090600</v>
       </c>
       <c r="J89" s="3">
-        <v>1131500</v>
+        <v>1163600</v>
       </c>
       <c r="K89" s="3">
         <v>384600</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-28300</v>
+        <v>-29200</v>
       </c>
       <c r="E91" s="3">
-        <v>-22500</v>
+        <v>-23200</v>
       </c>
       <c r="F91" s="3">
-        <v>-37700</v>
+        <v>-38800</v>
       </c>
       <c r="G91" s="3">
-        <v>-31100</v>
+        <v>-32000</v>
       </c>
       <c r="H91" s="3">
-        <v>-46100</v>
+        <v>-47400</v>
       </c>
       <c r="I91" s="3">
-        <v>-29700</v>
+        <v>-30600</v>
       </c>
       <c r="J91" s="3">
-        <v>-24600</v>
+        <v>-25300</v>
       </c>
       <c r="K91" s="3">
         <v>-31400</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-82000</v>
+        <v>-84300</v>
       </c>
       <c r="E94" s="3">
-        <v>-77000</v>
+        <v>-79200</v>
       </c>
       <c r="F94" s="3">
-        <v>-3074300</v>
+        <v>-3161400</v>
       </c>
       <c r="G94" s="3">
-        <v>222500</v>
+        <v>228800</v>
       </c>
       <c r="H94" s="3">
-        <v>-421400</v>
+        <v>-433400</v>
       </c>
       <c r="I94" s="3">
-        <v>441400</v>
+        <v>453900</v>
       </c>
       <c r="J94" s="3">
-        <v>-1250100</v>
+        <v>-1285500</v>
       </c>
       <c r="K94" s="3">
         <v>455600</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-918900</v>
+        <v>-945000</v>
       </c>
       <c r="E96" s="3">
-        <v>-572200</v>
+        <v>-588400</v>
       </c>
       <c r="F96" s="3">
-        <v>-233500</v>
+        <v>-240100</v>
       </c>
       <c r="G96" s="3">
-        <v>-371600</v>
+        <v>-382100</v>
       </c>
       <c r="H96" s="3">
-        <v>-377700</v>
+        <v>-388400</v>
       </c>
       <c r="I96" s="3">
-        <v>-396500</v>
+        <v>-407700</v>
       </c>
       <c r="J96" s="3">
-        <v>-362600</v>
+        <v>-372800</v>
       </c>
       <c r="K96" s="3">
         <v>-414300</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1633400</v>
+        <v>-1679600</v>
       </c>
       <c r="E100" s="3">
-        <v>-864100</v>
+        <v>-888600</v>
       </c>
       <c r="F100" s="3">
-        <v>1426600</v>
+        <v>1467000</v>
       </c>
       <c r="G100" s="3">
-        <v>1549300</v>
+        <v>1593100</v>
       </c>
       <c r="H100" s="3">
-        <v>850600</v>
+        <v>874700</v>
       </c>
       <c r="I100" s="3">
-        <v>683700</v>
+        <v>703000</v>
       </c>
       <c r="J100" s="3">
-        <v>140600</v>
+        <v>144600</v>
       </c>
       <c r="K100" s="3">
         <v>-804100</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>16600</v>
+        <v>17000</v>
       </c>
       <c r="E101" s="3">
-        <v>40300</v>
+        <v>41400</v>
       </c>
       <c r="F101" s="3">
-        <v>344500</v>
+        <v>354200</v>
       </c>
       <c r="G101" s="3">
-        <v>-36400</v>
+        <v>-37500</v>
       </c>
       <c r="H101" s="3">
-        <v>36400</v>
+        <v>37400</v>
       </c>
       <c r="I101" s="3">
-        <v>123100</v>
+        <v>126600</v>
       </c>
       <c r="J101" s="3">
-        <v>-40700</v>
+        <v>-41800</v>
       </c>
       <c r="K101" s="3">
         <v>-32600</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-594900</v>
+        <v>-611800</v>
       </c>
       <c r="E102" s="3">
-        <v>-1254400</v>
+        <v>-1289900</v>
       </c>
       <c r="F102" s="3">
-        <v>1272000</v>
+        <v>1308000</v>
       </c>
       <c r="G102" s="3">
-        <v>2286100</v>
+        <v>2350900</v>
       </c>
       <c r="H102" s="3">
-        <v>1775500</v>
+        <v>1825700</v>
       </c>
       <c r="I102" s="3">
-        <v>187600</v>
+        <v>192900</v>
       </c>
       <c r="J102" s="3">
-        <v>-18600</v>
+        <v>-19200</v>
       </c>
       <c r="K102" s="3">
         <v>3500</v>

--- a/AAII_Financials/Yearly/BCH_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BCH_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>4375800</v>
+        <v>4335700</v>
       </c>
       <c r="E8" s="3">
-        <v>4835600</v>
+        <v>4791200</v>
       </c>
       <c r="F8" s="3">
-        <v>2597500</v>
+        <v>2573600</v>
       </c>
       <c r="G8" s="3">
-        <v>2041600</v>
+        <v>2022900</v>
       </c>
       <c r="H8" s="3">
-        <v>2301700</v>
+        <v>2280600</v>
       </c>
       <c r="I8" s="3">
-        <v>2179500</v>
+        <v>2159500</v>
       </c>
       <c r="J8" s="3">
-        <v>2050800</v>
+        <v>2032000</v>
       </c>
       <c r="K8" s="3">
         <v>2160100</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-100600</v>
+        <v>-99700</v>
       </c>
       <c r="E15" s="3">
-        <v>-91800</v>
+        <v>-90900</v>
       </c>
       <c r="F15" s="3">
-        <v>-83700</v>
+        <v>-82900</v>
       </c>
       <c r="G15" s="3">
-        <v>-80000</v>
+        <v>-79200</v>
       </c>
       <c r="H15" s="3">
-        <v>-76900</v>
+        <v>-76200</v>
       </c>
       <c r="I15" s="3">
-        <v>-41100</v>
+        <v>-40700</v>
       </c>
       <c r="J15" s="3">
-        <v>-38400</v>
+        <v>-38100</v>
       </c>
       <c r="K15" s="3">
         <v>-37600</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2708200</v>
+        <v>2683400</v>
       </c>
       <c r="E17" s="3">
-        <v>2684900</v>
+        <v>2660200</v>
       </c>
       <c r="F17" s="3">
-        <v>1294600</v>
+        <v>1282700</v>
       </c>
       <c r="G17" s="3">
-        <v>1084500</v>
+        <v>1074600</v>
       </c>
       <c r="H17" s="3">
-        <v>1187600</v>
+        <v>1176700</v>
       </c>
       <c r="I17" s="3">
-        <v>1047500</v>
+        <v>1037900</v>
       </c>
       <c r="J17" s="3">
-        <v>966800</v>
+        <v>957900</v>
       </c>
       <c r="K17" s="3">
         <v>1130000</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1667600</v>
+        <v>1652300</v>
       </c>
       <c r="E18" s="3">
-        <v>2150700</v>
+        <v>2131000</v>
       </c>
       <c r="F18" s="3">
-        <v>1302900</v>
+        <v>1290900</v>
       </c>
       <c r="G18" s="3">
-        <v>957100</v>
+        <v>948300</v>
       </c>
       <c r="H18" s="3">
-        <v>1114100</v>
+        <v>1103900</v>
       </c>
       <c r="I18" s="3">
-        <v>1132000</v>
+        <v>1121600</v>
       </c>
       <c r="J18" s="3">
-        <v>1084000</v>
+        <v>1074000</v>
       </c>
       <c r="K18" s="3">
         <v>1030100</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-13500</v>
+        <v>-13400</v>
       </c>
       <c r="E20" s="3">
-        <v>-313800</v>
+        <v>-310900</v>
       </c>
       <c r="F20" s="3">
-        <v>-244000</v>
+        <v>-241700</v>
       </c>
       <c r="G20" s="3">
-        <v>-315000</v>
+        <v>-312100</v>
       </c>
       <c r="H20" s="3">
-        <v>-282800</v>
+        <v>-280200</v>
       </c>
       <c r="I20" s="3">
-        <v>-312900</v>
+        <v>-310100</v>
       </c>
       <c r="J20" s="3">
-        <v>-330700</v>
+        <v>-327700</v>
       </c>
       <c r="K20" s="3">
         <v>-305500</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1753800</v>
+        <v>1737700</v>
       </c>
       <c r="E21" s="3">
-        <v>1927800</v>
+        <v>1910100</v>
       </c>
       <c r="F21" s="3">
-        <v>1141800</v>
+        <v>1131400</v>
       </c>
       <c r="G21" s="3">
-        <v>721300</v>
+        <v>714700</v>
       </c>
       <c r="H21" s="3">
-        <v>907500</v>
+        <v>899200</v>
       </c>
       <c r="I21" s="3">
-        <v>859700</v>
+        <v>851800</v>
       </c>
       <c r="J21" s="3">
-        <v>791300</v>
+        <v>784000</v>
       </c>
       <c r="K21" s="3">
         <v>762300</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1654100</v>
+        <v>1638900</v>
       </c>
       <c r="E23" s="3">
-        <v>1836900</v>
+        <v>1820000</v>
       </c>
       <c r="F23" s="3">
-        <v>1058900</v>
+        <v>1049200</v>
       </c>
       <c r="G23" s="3">
-        <v>642100</v>
+        <v>636200</v>
       </c>
       <c r="H23" s="3">
-        <v>831300</v>
+        <v>823700</v>
       </c>
       <c r="I23" s="3">
-        <v>819000</v>
+        <v>811500</v>
       </c>
       <c r="J23" s="3">
-        <v>753200</v>
+        <v>746300</v>
       </c>
       <c r="K23" s="3">
         <v>724700</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>298500</v>
+        <v>295800</v>
       </c>
       <c r="E24" s="3">
-        <v>300600</v>
+        <v>297800</v>
       </c>
       <c r="F24" s="3">
-        <v>194600</v>
+        <v>192800</v>
       </c>
       <c r="G24" s="3">
-        <v>137300</v>
+        <v>136000</v>
       </c>
       <c r="H24" s="3">
-        <v>185000</v>
+        <v>183300</v>
       </c>
       <c r="I24" s="3">
-        <v>170600</v>
+        <v>169100</v>
       </c>
       <c r="J24" s="3">
-        <v>125400</v>
+        <v>124200</v>
       </c>
       <c r="K24" s="3">
         <v>100600</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1355600</v>
+        <v>1343100</v>
       </c>
       <c r="E26" s="3">
-        <v>1536300</v>
+        <v>1522200</v>
       </c>
       <c r="F26" s="3">
-        <v>864300</v>
+        <v>856400</v>
       </c>
       <c r="G26" s="3">
-        <v>504800</v>
+        <v>500200</v>
       </c>
       <c r="H26" s="3">
-        <v>646400</v>
+        <v>640400</v>
       </c>
       <c r="I26" s="3">
-        <v>648400</v>
+        <v>642500</v>
       </c>
       <c r="J26" s="3">
-        <v>627900</v>
+        <v>622100</v>
       </c>
       <c r="K26" s="3">
         <v>624000</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1355600</v>
+        <v>1343100</v>
       </c>
       <c r="E27" s="3">
-        <v>1536300</v>
+        <v>1522200</v>
       </c>
       <c r="F27" s="3">
-        <v>864300</v>
+        <v>856400</v>
       </c>
       <c r="G27" s="3">
-        <v>504800</v>
+        <v>500200</v>
       </c>
       <c r="H27" s="3">
-        <v>646400</v>
+        <v>640400</v>
       </c>
       <c r="I27" s="3">
-        <v>648400</v>
+        <v>642500</v>
       </c>
       <c r="J27" s="3">
-        <v>627900</v>
+        <v>622100</v>
       </c>
       <c r="K27" s="3">
         <v>624000</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>13500</v>
+        <v>13400</v>
       </c>
       <c r="E32" s="3">
-        <v>313800</v>
+        <v>310900</v>
       </c>
       <c r="F32" s="3">
-        <v>244000</v>
+        <v>241700</v>
       </c>
       <c r="G32" s="3">
-        <v>315000</v>
+        <v>312100</v>
       </c>
       <c r="H32" s="3">
-        <v>282800</v>
+        <v>280200</v>
       </c>
       <c r="I32" s="3">
-        <v>312900</v>
+        <v>310100</v>
       </c>
       <c r="J32" s="3">
-        <v>330700</v>
+        <v>327700</v>
       </c>
       <c r="K32" s="3">
         <v>305500</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1355600</v>
+        <v>1343100</v>
       </c>
       <c r="E33" s="3">
-        <v>1536300</v>
+        <v>1522200</v>
       </c>
       <c r="F33" s="3">
-        <v>864300</v>
+        <v>856400</v>
       </c>
       <c r="G33" s="3">
-        <v>504800</v>
+        <v>500200</v>
       </c>
       <c r="H33" s="3">
-        <v>646400</v>
+        <v>640400</v>
       </c>
       <c r="I33" s="3">
-        <v>648400</v>
+        <v>642500</v>
       </c>
       <c r="J33" s="3">
-        <v>627900</v>
+        <v>622100</v>
       </c>
       <c r="K33" s="3">
         <v>624000</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1355600</v>
+        <v>1343100</v>
       </c>
       <c r="E35" s="3">
-        <v>1536300</v>
+        <v>1522200</v>
       </c>
       <c r="F35" s="3">
-        <v>864300</v>
+        <v>856400</v>
       </c>
       <c r="G35" s="3">
-        <v>504800</v>
+        <v>500200</v>
       </c>
       <c r="H35" s="3">
-        <v>646400</v>
+        <v>640400</v>
       </c>
       <c r="I35" s="3">
-        <v>648400</v>
+        <v>642500</v>
       </c>
       <c r="J35" s="3">
-        <v>627900</v>
+        <v>622100</v>
       </c>
       <c r="K35" s="3">
         <v>624000</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>4855000</v>
+        <v>4810500</v>
       </c>
       <c r="E41" s="3">
-        <v>4663200</v>
+        <v>4620500</v>
       </c>
       <c r="F41" s="3">
-        <v>5150100</v>
+        <v>5102800</v>
       </c>
       <c r="G41" s="3">
-        <v>5209100</v>
+        <v>5161400</v>
       </c>
       <c r="H41" s="3">
-        <v>3043800</v>
+        <v>3015800</v>
       </c>
       <c r="I41" s="3">
-        <v>3075200</v>
+        <v>3047000</v>
       </c>
       <c r="J41" s="3">
-        <v>2143800</v>
+        <v>2124100</v>
       </c>
       <c r="K41" s="3">
         <v>2636400</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>5274500</v>
+        <v>5226100</v>
       </c>
       <c r="E42" s="3">
-        <v>5673700</v>
+        <v>5621600</v>
       </c>
       <c r="F42" s="3">
-        <v>8740700</v>
+        <v>8660500</v>
       </c>
       <c r="G42" s="3">
-        <v>9442700</v>
+        <v>9356100</v>
       </c>
       <c r="H42" s="3">
-        <v>6676000</v>
+        <v>6614700</v>
       </c>
       <c r="I42" s="3">
-        <v>3804100</v>
+        <v>3769200</v>
       </c>
       <c r="J42" s="3">
-        <v>3627800</v>
+        <v>3594500</v>
       </c>
       <c r="K42" s="3">
         <v>2356800</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>83900</v>
+        <v>83200</v>
       </c>
       <c r="E47" s="3">
-        <v>67800</v>
+        <v>67200</v>
       </c>
       <c r="F47" s="3">
-        <v>53600</v>
+        <v>53100</v>
       </c>
       <c r="G47" s="3">
-        <v>48700</v>
+        <v>48200</v>
       </c>
       <c r="H47" s="3">
-        <v>55300</v>
+        <v>54800</v>
       </c>
       <c r="I47" s="3">
-        <v>48600</v>
+        <v>48100</v>
       </c>
       <c r="J47" s="3">
-        <v>41500</v>
+        <v>41100</v>
       </c>
       <c r="K47" s="3">
         <v>36800</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>351300</v>
+        <v>348100</v>
       </c>
       <c r="E48" s="3">
-        <v>345700</v>
+        <v>342500</v>
       </c>
       <c r="F48" s="3">
-        <v>365100</v>
+        <v>361800</v>
       </c>
       <c r="G48" s="3">
-        <v>381100</v>
+        <v>377600</v>
       </c>
       <c r="H48" s="3">
-        <v>418700</v>
+        <v>414800</v>
       </c>
       <c r="I48" s="3">
-        <v>250500</v>
+        <v>248200</v>
       </c>
       <c r="J48" s="3">
-        <v>251300</v>
+        <v>249000</v>
       </c>
       <c r="K48" s="3">
         <v>264100</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>149600</v>
+        <v>148200</v>
       </c>
       <c r="E49" s="3">
-        <v>116200</v>
+        <v>115100</v>
       </c>
       <c r="F49" s="3">
-        <v>79100</v>
+        <v>78300</v>
       </c>
       <c r="G49" s="3">
-        <v>66200</v>
+        <v>65600</v>
       </c>
       <c r="H49" s="3">
-        <v>63600</v>
+        <v>63000</v>
       </c>
       <c r="I49" s="3">
-        <v>56700</v>
+        <v>56200</v>
       </c>
       <c r="J49" s="3">
-        <v>42600</v>
+        <v>42200</v>
       </c>
       <c r="K49" s="3">
         <v>33200</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>613400</v>
+        <v>607700</v>
       </c>
       <c r="E52" s="3">
-        <v>599900</v>
+        <v>594400</v>
       </c>
       <c r="F52" s="3">
-        <v>478700</v>
+        <v>474300</v>
       </c>
       <c r="G52" s="3">
-        <v>390200</v>
+        <v>386600</v>
       </c>
       <c r="H52" s="3">
-        <v>349800</v>
+        <v>346600</v>
       </c>
       <c r="I52" s="3">
-        <v>302900</v>
+        <v>300200</v>
       </c>
       <c r="J52" s="3">
-        <v>291500</v>
+        <v>288800</v>
       </c>
       <c r="K52" s="3">
         <v>318300</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>60813900</v>
+        <v>60256000</v>
       </c>
       <c r="E54" s="3">
-        <v>60228300</v>
+        <v>59675800</v>
       </c>
       <c r="F54" s="3">
-        <v>56355700</v>
+        <v>55838600</v>
       </c>
       <c r="G54" s="3">
-        <v>50243700</v>
+        <v>49782700</v>
       </c>
       <c r="H54" s="3">
-        <v>44987900</v>
+        <v>44575200</v>
       </c>
       <c r="I54" s="3">
-        <v>39159800</v>
+        <v>38800600</v>
       </c>
       <c r="J54" s="3">
-        <v>35778400</v>
+        <v>35450100</v>
       </c>
       <c r="K54" s="3">
         <v>35633100</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>762100</v>
+        <v>755100</v>
       </c>
       <c r="E57" s="3">
-        <v>1305300</v>
+        <v>1293300</v>
       </c>
       <c r="F57" s="3">
-        <v>742200</v>
+        <v>735400</v>
       </c>
       <c r="G57" s="3">
-        <v>1716900</v>
+        <v>1701200</v>
       </c>
       <c r="H57" s="3">
-        <v>636100</v>
+        <v>630300</v>
       </c>
       <c r="I57" s="3">
-        <v>558500</v>
+        <v>553400</v>
       </c>
       <c r="J57" s="3">
-        <v>529600</v>
+        <v>524700</v>
       </c>
       <c r="K57" s="3">
         <v>385800</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3098900</v>
+        <v>3070500</v>
       </c>
       <c r="E58" s="3">
-        <v>3506300</v>
+        <v>3474200</v>
       </c>
       <c r="F58" s="3">
-        <v>3655400</v>
+        <v>3621900</v>
       </c>
       <c r="G58" s="3">
-        <v>2630900</v>
+        <v>2606800</v>
       </c>
       <c r="H58" s="3">
-        <v>3411200</v>
+        <v>3379900</v>
       </c>
       <c r="I58" s="3">
-        <v>3374300</v>
+        <v>3343300</v>
       </c>
       <c r="J58" s="3">
-        <v>2738700</v>
+        <v>2713600</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>5</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>691200</v>
+        <v>684800</v>
       </c>
       <c r="E59" s="3">
-        <v>581900</v>
+        <v>576500</v>
       </c>
       <c r="F59" s="3">
-        <v>482000</v>
+        <v>477500</v>
       </c>
       <c r="G59" s="3">
-        <v>245100</v>
+        <v>242900</v>
       </c>
       <c r="H59" s="3">
-        <v>412200</v>
+        <v>408400</v>
       </c>
       <c r="I59" s="3">
-        <v>356900</v>
+        <v>353600</v>
       </c>
       <c r="J59" s="3">
-        <v>346100</v>
+        <v>342900</v>
       </c>
       <c r="K59" s="3">
         <v>323900</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>14731900</v>
+        <v>14596700</v>
       </c>
       <c r="E61" s="3">
-        <v>14289200</v>
+        <v>14158100</v>
       </c>
       <c r="F61" s="3">
-        <v>12483200</v>
+        <v>12368700</v>
       </c>
       <c r="G61" s="3">
-        <v>11385400</v>
+        <v>11280900</v>
       </c>
       <c r="H61" s="3">
-        <v>8565400</v>
+        <v>8486800</v>
       </c>
       <c r="I61" s="3">
-        <v>6887100</v>
+        <v>6824000</v>
       </c>
       <c r="J61" s="3">
-        <v>5999300</v>
+        <v>5944300</v>
       </c>
       <c r="K61" s="3">
         <v>8366700</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1047800</v>
+        <v>1038200</v>
       </c>
       <c r="E62" s="3">
-        <v>1026600</v>
+        <v>1017100</v>
       </c>
       <c r="F62" s="3">
-        <v>789300</v>
+        <v>782000</v>
       </c>
       <c r="G62" s="3">
-        <v>559900</v>
+        <v>554700</v>
       </c>
       <c r="H62" s="3">
-        <v>418800</v>
+        <v>414900</v>
       </c>
       <c r="I62" s="3">
-        <v>397500</v>
+        <v>393900</v>
       </c>
       <c r="J62" s="3">
-        <v>417400</v>
+        <v>413600</v>
       </c>
       <c r="K62" s="3">
         <v>425800</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>55105200</v>
+        <v>54599700</v>
       </c>
       <c r="E66" s="3">
-        <v>54932800</v>
+        <v>54428800</v>
       </c>
       <c r="F66" s="3">
-        <v>51752600</v>
+        <v>51277800</v>
       </c>
       <c r="G66" s="3">
-        <v>46182100</v>
+        <v>45758400</v>
       </c>
       <c r="H66" s="3">
-        <v>41142200</v>
+        <v>40764700</v>
       </c>
       <c r="I66" s="3">
-        <v>35558300</v>
+        <v>35232100</v>
       </c>
       <c r="J66" s="3">
-        <v>32393100</v>
+        <v>32096000</v>
       </c>
       <c r="K66" s="3">
         <v>32370300</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>3040000</v>
+        <v>3012100</v>
       </c>
       <c r="E72" s="3">
-        <v>2766500</v>
+        <v>2741100</v>
       </c>
       <c r="F72" s="3">
-        <v>1963800</v>
+        <v>1945700</v>
       </c>
       <c r="G72" s="3">
-        <v>1501300</v>
+        <v>1487500</v>
       </c>
       <c r="H72" s="3">
-        <v>1293400</v>
+        <v>1281500</v>
       </c>
       <c r="I72" s="3">
-        <v>1023200</v>
+        <v>1013800</v>
       </c>
       <c r="J72" s="3">
-        <v>921100</v>
+        <v>912600</v>
       </c>
       <c r="K72" s="3">
         <v>876900</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>5708600</v>
+        <v>5656300</v>
       </c>
       <c r="E76" s="3">
-        <v>5295600</v>
+        <v>5247000</v>
       </c>
       <c r="F76" s="3">
-        <v>4603100</v>
+        <v>4560900</v>
       </c>
       <c r="G76" s="3">
-        <v>4061600</v>
+        <v>4024400</v>
       </c>
       <c r="H76" s="3">
-        <v>3845800</v>
+        <v>3810500</v>
       </c>
       <c r="I76" s="3">
-        <v>3601500</v>
+        <v>3568500</v>
       </c>
       <c r="J76" s="3">
-        <v>3385200</v>
+        <v>3354200</v>
       </c>
       <c r="K76" s="3">
         <v>3262800</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1355600</v>
+        <v>1343100</v>
       </c>
       <c r="E81" s="3">
-        <v>1536300</v>
+        <v>1522200</v>
       </c>
       <c r="F81" s="3">
-        <v>864300</v>
+        <v>856400</v>
       </c>
       <c r="G81" s="3">
-        <v>504800</v>
+        <v>500200</v>
       </c>
       <c r="H81" s="3">
-        <v>646400</v>
+        <v>640400</v>
       </c>
       <c r="I81" s="3">
-        <v>648400</v>
+        <v>642500</v>
       </c>
       <c r="J81" s="3">
-        <v>627900</v>
+        <v>622100</v>
       </c>
       <c r="K81" s="3">
         <v>624000</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100600</v>
+        <v>99700</v>
       </c>
       <c r="E83" s="3">
-        <v>91800</v>
+        <v>90900</v>
       </c>
       <c r="F83" s="3">
-        <v>83700</v>
+        <v>82900</v>
       </c>
       <c r="G83" s="3">
-        <v>80000</v>
+        <v>79200</v>
       </c>
       <c r="H83" s="3">
-        <v>76900</v>
+        <v>76200</v>
       </c>
       <c r="I83" s="3">
-        <v>41100</v>
+        <v>40700</v>
       </c>
       <c r="J83" s="3">
-        <v>38400</v>
+        <v>38100</v>
       </c>
       <c r="K83" s="3">
         <v>37600</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1135100</v>
+        <v>1124700</v>
       </c>
       <c r="E89" s="3">
-        <v>-363600</v>
+        <v>-360300</v>
       </c>
       <c r="F89" s="3">
-        <v>2648100</v>
+        <v>2623800</v>
       </c>
       <c r="G89" s="3">
-        <v>566400</v>
+        <v>561200</v>
       </c>
       <c r="H89" s="3">
-        <v>1347100</v>
+        <v>1334700</v>
       </c>
       <c r="I89" s="3">
-        <v>-1090600</v>
+        <v>-1080600</v>
       </c>
       <c r="J89" s="3">
-        <v>1163600</v>
+        <v>1152900</v>
       </c>
       <c r="K89" s="3">
         <v>384600</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-29200</v>
+        <v>-28900</v>
       </c>
       <c r="E91" s="3">
-        <v>-23200</v>
+        <v>-22900</v>
       </c>
       <c r="F91" s="3">
-        <v>-38800</v>
+        <v>-38400</v>
       </c>
       <c r="G91" s="3">
-        <v>-32000</v>
+        <v>-31700</v>
       </c>
       <c r="H91" s="3">
-        <v>-47400</v>
+        <v>-47000</v>
       </c>
       <c r="I91" s="3">
-        <v>-30600</v>
+        <v>-30300</v>
       </c>
       <c r="J91" s="3">
-        <v>-25300</v>
+        <v>-25100</v>
       </c>
       <c r="K91" s="3">
         <v>-31400</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-84300</v>
+        <v>-83600</v>
       </c>
       <c r="E94" s="3">
-        <v>-79200</v>
+        <v>-78400</v>
       </c>
       <c r="F94" s="3">
-        <v>-3161400</v>
+        <v>-3132300</v>
       </c>
       <c r="G94" s="3">
-        <v>228800</v>
+        <v>226700</v>
       </c>
       <c r="H94" s="3">
-        <v>-433400</v>
+        <v>-429400</v>
       </c>
       <c r="I94" s="3">
-        <v>453900</v>
+        <v>449800</v>
       </c>
       <c r="J94" s="3">
-        <v>-1285500</v>
+        <v>-1273700</v>
       </c>
       <c r="K94" s="3">
         <v>455600</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-945000</v>
+        <v>-936300</v>
       </c>
       <c r="E96" s="3">
-        <v>-588400</v>
+        <v>-583000</v>
       </c>
       <c r="F96" s="3">
-        <v>-240100</v>
+        <v>-237900</v>
       </c>
       <c r="G96" s="3">
-        <v>-382100</v>
+        <v>-378600</v>
       </c>
       <c r="H96" s="3">
-        <v>-388400</v>
+        <v>-384800</v>
       </c>
       <c r="I96" s="3">
-        <v>-407700</v>
+        <v>-404000</v>
       </c>
       <c r="J96" s="3">
-        <v>-372800</v>
+        <v>-369400</v>
       </c>
       <c r="K96" s="3">
         <v>-414300</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1679600</v>
+        <v>-1664200</v>
       </c>
       <c r="E100" s="3">
-        <v>-888600</v>
+        <v>-880400</v>
       </c>
       <c r="F100" s="3">
-        <v>1467000</v>
+        <v>1453500</v>
       </c>
       <c r="G100" s="3">
-        <v>1593100</v>
+        <v>1578500</v>
       </c>
       <c r="H100" s="3">
-        <v>874700</v>
+        <v>866600</v>
       </c>
       <c r="I100" s="3">
-        <v>703000</v>
+        <v>696600</v>
       </c>
       <c r="J100" s="3">
-        <v>144600</v>
+        <v>143300</v>
       </c>
       <c r="K100" s="3">
         <v>-804100</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>17000</v>
+        <v>16900</v>
       </c>
       <c r="E101" s="3">
-        <v>41400</v>
+        <v>41100</v>
       </c>
       <c r="F101" s="3">
-        <v>354200</v>
+        <v>351000</v>
       </c>
       <c r="G101" s="3">
-        <v>-37500</v>
+        <v>-37100</v>
       </c>
       <c r="H101" s="3">
-        <v>37400</v>
+        <v>37000</v>
       </c>
       <c r="I101" s="3">
-        <v>126600</v>
+        <v>125400</v>
       </c>
       <c r="J101" s="3">
-        <v>-41800</v>
+        <v>-41400</v>
       </c>
       <c r="K101" s="3">
         <v>-32600</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-611800</v>
+        <v>-606100</v>
       </c>
       <c r="E102" s="3">
-        <v>-1289900</v>
+        <v>-1278100</v>
       </c>
       <c r="F102" s="3">
-        <v>1308000</v>
+        <v>1296000</v>
       </c>
       <c r="G102" s="3">
-        <v>2350900</v>
+        <v>2329300</v>
       </c>
       <c r="H102" s="3">
-        <v>1825700</v>
+        <v>1809000</v>
       </c>
       <c r="I102" s="3">
-        <v>192900</v>
+        <v>191100</v>
       </c>
       <c r="J102" s="3">
-        <v>-19200</v>
+        <v>-19000</v>
       </c>
       <c r="K102" s="3">
         <v>3500</v>

--- a/AAII_Financials/Yearly/BCH_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BCH_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
   <si>
     <t>BCH</t>
   </si>
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>4335700</v>
+        <v>3210500</v>
       </c>
       <c r="E8" s="3">
-        <v>4791200</v>
+        <v>3214000</v>
       </c>
       <c r="F8" s="3">
-        <v>2573600</v>
+        <v>2588800</v>
       </c>
       <c r="G8" s="3">
-        <v>2022900</v>
+        <v>2077500</v>
       </c>
       <c r="H8" s="3">
-        <v>2280600</v>
+        <v>2217300</v>
       </c>
       <c r="I8" s="3">
-        <v>2159500</v>
+        <v>2294000</v>
       </c>
       <c r="J8" s="3">
-        <v>2032000</v>
+        <v>2395400</v>
       </c>
       <c r="K8" s="3">
         <v>2160100</v>
@@ -770,26 +770,26 @@
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
+      <c r="D9" s="3">
+        <v>56600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>49600</v>
+      </c>
+      <c r="F9" s="3">
+        <v>46600</v>
+      </c>
+      <c r="G9" s="3">
+        <v>67900</v>
+      </c>
+      <c r="H9" s="3">
+        <v>68500</v>
+      </c>
+      <c r="I9" s="3">
+        <v>55400</v>
+      </c>
+      <c r="J9" s="3">
+        <v>58200</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>5</v>
@@ -815,26 +815,26 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>3153900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3164400</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2542300</v>
+      </c>
+      <c r="G10" s="3">
+        <v>2009600</v>
+      </c>
+      <c r="H10" s="3">
+        <v>2148800</v>
+      </c>
+      <c r="I10" s="3">
+        <v>2238600</v>
+      </c>
+      <c r="J10" s="3">
+        <v>2337100</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -970,25 +970,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-99700</v>
+        <v>35100</v>
       </c>
       <c r="E15" s="3">
-        <v>-90900</v>
+        <v>36400</v>
       </c>
       <c r="F15" s="3">
-        <v>-82900</v>
+        <v>34900</v>
       </c>
       <c r="G15" s="3">
-        <v>-79200</v>
+        <v>42000</v>
       </c>
       <c r="H15" s="3">
-        <v>-76200</v>
+        <v>38800</v>
       </c>
       <c r="I15" s="3">
-        <v>-40700</v>
+        <v>39200</v>
       </c>
       <c r="J15" s="3">
-        <v>-38100</v>
+        <v>42500</v>
       </c>
       <c r="K15" s="3">
         <v>-37600</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2683400</v>
+        <v>1273600</v>
       </c>
       <c r="E17" s="3">
-        <v>2660200</v>
+        <v>1171600</v>
       </c>
       <c r="F17" s="3">
-        <v>1282700</v>
+        <v>1023100</v>
       </c>
       <c r="G17" s="3">
-        <v>1074600</v>
+        <v>1239200</v>
       </c>
       <c r="H17" s="3">
-        <v>1176700</v>
+        <v>1208000</v>
       </c>
       <c r="I17" s="3">
-        <v>1037900</v>
+        <v>1221000</v>
       </c>
       <c r="J17" s="3">
-        <v>957900</v>
+        <v>1281900</v>
       </c>
       <c r="K17" s="3">
         <v>1130000</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1652300</v>
+        <v>1936900</v>
       </c>
       <c r="E18" s="3">
-        <v>2131000</v>
+        <v>2042500</v>
       </c>
       <c r="F18" s="3">
-        <v>1290900</v>
+        <v>1565700</v>
       </c>
       <c r="G18" s="3">
-        <v>948300</v>
+        <v>838300</v>
       </c>
       <c r="H18" s="3">
-        <v>1103900</v>
+        <v>1009300</v>
       </c>
       <c r="I18" s="3">
-        <v>1121600</v>
+        <v>1073000</v>
       </c>
       <c r="J18" s="3">
-        <v>1074000</v>
+        <v>1113500</v>
       </c>
       <c r="K18" s="3">
         <v>1030100</v>
@@ -1184,26 +1184,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-13400</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-310900</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-241700</v>
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G20" s="3">
-        <v>-312100</v>
+        <v>6600</v>
       </c>
       <c r="H20" s="3">
-        <v>-280200</v>
+        <v>-8600</v>
       </c>
       <c r="I20" s="3">
-        <v>-310100</v>
+        <v>-10500</v>
       </c>
       <c r="J20" s="3">
-        <v>-327700</v>
+        <v>-9800</v>
       </c>
       <c r="K20" s="3">
         <v>-305500</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1737700</v>
+        <v>1971900</v>
       </c>
       <c r="E21" s="3">
-        <v>1910100</v>
+        <v>2078900</v>
       </c>
       <c r="F21" s="3">
-        <v>1131400</v>
+        <v>1600600</v>
       </c>
       <c r="G21" s="3">
-        <v>714700</v>
+        <v>873700</v>
       </c>
       <c r="H21" s="3">
-        <v>899200</v>
+        <v>1056700</v>
       </c>
       <c r="I21" s="3">
-        <v>851800</v>
+        <v>1122700</v>
       </c>
       <c r="J21" s="3">
-        <v>784000</v>
+        <v>1165900</v>
       </c>
       <c r="K21" s="3">
         <v>762300</v>
@@ -1274,26 +1274,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1638900</v>
+        <v>1934700</v>
       </c>
       <c r="E23" s="3">
-        <v>1820000</v>
+        <v>2042300</v>
       </c>
       <c r="F23" s="3">
-        <v>1049200</v>
+        <v>1563700</v>
       </c>
       <c r="G23" s="3">
-        <v>636200</v>
+        <v>829100</v>
       </c>
       <c r="H23" s="3">
-        <v>823700</v>
+        <v>1014300</v>
       </c>
       <c r="I23" s="3">
-        <v>811500</v>
+        <v>1082800</v>
       </c>
       <c r="J23" s="3">
-        <v>746300</v>
+        <v>1122800</v>
       </c>
       <c r="K23" s="3">
         <v>724700</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>295800</v>
+        <v>367400</v>
       </c>
       <c r="E24" s="3">
-        <v>297800</v>
+        <v>340400</v>
       </c>
       <c r="F24" s="3">
-        <v>192800</v>
+        <v>323900</v>
       </c>
       <c r="G24" s="3">
-        <v>136000</v>
+        <v>177300</v>
       </c>
       <c r="H24" s="3">
-        <v>183300</v>
+        <v>225700</v>
       </c>
       <c r="I24" s="3">
-        <v>169100</v>
+        <v>225600</v>
       </c>
       <c r="J24" s="3">
-        <v>124200</v>
+        <v>186900</v>
       </c>
       <c r="K24" s="3">
         <v>100600</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1343100</v>
+        <v>1567300</v>
       </c>
       <c r="E26" s="3">
-        <v>1522200</v>
+        <v>1701800</v>
       </c>
       <c r="F26" s="3">
-        <v>856400</v>
+        <v>1239800</v>
       </c>
       <c r="G26" s="3">
-        <v>500200</v>
+        <v>651800</v>
       </c>
       <c r="H26" s="3">
-        <v>640400</v>
+        <v>788700</v>
       </c>
       <c r="I26" s="3">
-        <v>642500</v>
+        <v>857300</v>
       </c>
       <c r="J26" s="3">
-        <v>622100</v>
+        <v>935900</v>
       </c>
       <c r="K26" s="3">
         <v>624000</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1343100</v>
+        <v>1567300</v>
       </c>
       <c r="E27" s="3">
-        <v>1522200</v>
+        <v>1701800</v>
       </c>
       <c r="F27" s="3">
-        <v>856400</v>
+        <v>1239800</v>
       </c>
       <c r="G27" s="3">
-        <v>500200</v>
+        <v>651800</v>
       </c>
       <c r="H27" s="3">
-        <v>640400</v>
+        <v>788700</v>
       </c>
       <c r="I27" s="3">
-        <v>642500</v>
+        <v>857300</v>
       </c>
       <c r="J27" s="3">
-        <v>622100</v>
+        <v>935900</v>
       </c>
       <c r="K27" s="3">
         <v>624000</v>
@@ -1724,26 +1724,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>13400</v>
-      </c>
-      <c r="E32" s="3">
-        <v>310900</v>
-      </c>
-      <c r="F32" s="3">
-        <v>241700</v>
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G32" s="3">
-        <v>312100</v>
+        <v>-6600</v>
       </c>
       <c r="H32" s="3">
-        <v>280200</v>
+        <v>8600</v>
       </c>
       <c r="I32" s="3">
-        <v>310100</v>
+        <v>10500</v>
       </c>
       <c r="J32" s="3">
-        <v>327700</v>
+        <v>9800</v>
       </c>
       <c r="K32" s="3">
         <v>305500</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1343100</v>
+        <v>1567300</v>
       </c>
       <c r="E33" s="3">
-        <v>1522200</v>
+        <v>1701800</v>
       </c>
       <c r="F33" s="3">
-        <v>856400</v>
+        <v>1239800</v>
       </c>
       <c r="G33" s="3">
-        <v>500200</v>
+        <v>651800</v>
       </c>
       <c r="H33" s="3">
-        <v>640400</v>
+        <v>788700</v>
       </c>
       <c r="I33" s="3">
-        <v>642500</v>
+        <v>857300</v>
       </c>
       <c r="J33" s="3">
-        <v>622100</v>
+        <v>935900</v>
       </c>
       <c r="K33" s="3">
         <v>624000</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1343100</v>
+        <v>1567300</v>
       </c>
       <c r="E35" s="3">
-        <v>1522200</v>
+        <v>1701800</v>
       </c>
       <c r="F35" s="3">
-        <v>856400</v>
+        <v>1239800</v>
       </c>
       <c r="G35" s="3">
-        <v>500200</v>
+        <v>651800</v>
       </c>
       <c r="H35" s="3">
-        <v>640400</v>
+        <v>788700</v>
       </c>
       <c r="I35" s="3">
-        <v>642500</v>
+        <v>857300</v>
       </c>
       <c r="J35" s="3">
-        <v>622100</v>
+        <v>935900</v>
       </c>
       <c r="K35" s="3">
         <v>624000</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>4810500</v>
+        <v>2611700</v>
       </c>
       <c r="E41" s="3">
-        <v>4620500</v>
+        <v>3711200</v>
       </c>
       <c r="F41" s="3">
-        <v>5102800</v>
+        <v>3116200</v>
       </c>
       <c r="G41" s="3">
-        <v>5161400</v>
+        <v>2652800</v>
       </c>
       <c r="H41" s="3">
-        <v>3015800</v>
+        <v>2538200</v>
       </c>
       <c r="I41" s="3">
-        <v>3047000</v>
+        <v>2554500</v>
       </c>
       <c r="J41" s="3">
-        <v>2124100</v>
+        <v>2620700</v>
       </c>
       <c r="K41" s="3">
         <v>2636400</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>5226100</v>
+        <v>9159600</v>
       </c>
       <c r="E42" s="3">
-        <v>5621600</v>
+        <v>10045300</v>
       </c>
       <c r="F42" s="3">
-        <v>8660500</v>
+        <v>9406500</v>
       </c>
       <c r="G42" s="3">
-        <v>9356100</v>
+        <v>14674200</v>
       </c>
       <c r="H42" s="3">
-        <v>6614700</v>
+        <v>8503800</v>
       </c>
       <c r="I42" s="3">
-        <v>3769200</v>
+        <v>4754300</v>
       </c>
       <c r="J42" s="3">
-        <v>3594500</v>
+        <v>2229300</v>
       </c>
       <c r="K42" s="3">
         <v>2356800</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>841600</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>602900</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>371200</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>169900</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>141500</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>153400</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>267100</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>0</v>
+        <v>29000</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
+        <v>18100</v>
       </c>
       <c r="G44" s="3">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
+        <v>17300</v>
       </c>
       <c r="I44" s="3">
-        <v>0</v>
+        <v>25600</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>22800</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2172,26 +2172,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>4600</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>347400</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>737100</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>509400</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>311600</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>13767200</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>15250900</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>15130900</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>19665200</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>13405200</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>9127100</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>6584600</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>83200</v>
+        <v>6039200</v>
       </c>
       <c r="E47" s="3">
-        <v>67200</v>
+        <v>5806000</v>
       </c>
       <c r="F47" s="3">
-        <v>53100</v>
+        <v>4633000</v>
       </c>
       <c r="G47" s="3">
-        <v>48200</v>
+        <v>590800</v>
       </c>
       <c r="H47" s="3">
-        <v>54800</v>
+        <v>515700</v>
       </c>
       <c r="I47" s="3">
-        <v>48100</v>
+        <v>1751400</v>
       </c>
       <c r="J47" s="3">
-        <v>41100</v>
+        <v>3983400</v>
       </c>
       <c r="K47" s="3">
         <v>36800</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>348100</v>
+        <v>354200</v>
       </c>
       <c r="E48" s="3">
-        <v>342500</v>
+        <v>359100</v>
       </c>
       <c r="F48" s="3">
-        <v>361800</v>
+        <v>378500</v>
       </c>
       <c r="G48" s="3">
-        <v>377600</v>
+        <v>474000</v>
       </c>
       <c r="H48" s="3">
-        <v>414800</v>
+        <v>493300</v>
       </c>
       <c r="I48" s="3">
-        <v>248200</v>
+        <v>311100</v>
       </c>
       <c r="J48" s="3">
-        <v>249000</v>
+        <v>351400</v>
       </c>
       <c r="K48" s="3">
         <v>264100</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>148200</v>
+        <v>194600</v>
       </c>
       <c r="E49" s="3">
-        <v>115100</v>
+        <v>164800</v>
       </c>
       <c r="F49" s="3">
-        <v>78300</v>
+        <v>85100</v>
       </c>
       <c r="G49" s="3">
-        <v>65600</v>
+        <v>85400</v>
       </c>
       <c r="H49" s="3">
-        <v>63000</v>
+        <v>77500</v>
       </c>
       <c r="I49" s="3">
-        <v>56200</v>
+        <v>75000</v>
       </c>
       <c r="J49" s="3">
-        <v>42200</v>
+        <v>63400</v>
       </c>
       <c r="K49" s="3">
         <v>33200</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>607700</v>
+        <v>220500</v>
       </c>
       <c r="E52" s="3">
-        <v>594400</v>
+        <v>153000</v>
       </c>
       <c r="F52" s="3">
-        <v>474300</v>
+        <v>163100</v>
       </c>
       <c r="G52" s="3">
-        <v>386600</v>
+        <v>279800</v>
       </c>
       <c r="H52" s="3">
-        <v>346600</v>
+        <v>282400</v>
       </c>
       <c r="I52" s="3">
-        <v>300200</v>
+        <v>188100</v>
       </c>
       <c r="J52" s="3">
-        <v>288800</v>
+        <v>822200</v>
       </c>
       <c r="K52" s="3">
         <v>318300</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>60256000</v>
+        <v>63553600</v>
       </c>
       <c r="E54" s="3">
-        <v>59675800</v>
+        <v>64868300</v>
       </c>
       <c r="F54" s="3">
-        <v>55838600</v>
+        <v>60749200</v>
       </c>
       <c r="G54" s="3">
-        <v>49782700</v>
+        <v>64877000</v>
       </c>
       <c r="H54" s="3">
-        <v>44575200</v>
+        <v>54890600</v>
       </c>
       <c r="I54" s="3">
-        <v>38800600</v>
+        <v>51773200</v>
       </c>
       <c r="J54" s="3">
-        <v>35450100</v>
+        <v>53331500</v>
       </c>
       <c r="K54" s="3">
         <v>35633100</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>755100</v>
+        <v>33700900</v>
       </c>
       <c r="E57" s="3">
-        <v>1293300</v>
+        <v>33347900</v>
       </c>
       <c r="F57" s="3">
-        <v>735400</v>
+        <v>32136200</v>
       </c>
       <c r="G57" s="3">
-        <v>1701200</v>
+        <v>34257400</v>
       </c>
       <c r="H57" s="3">
-        <v>630300</v>
+        <v>29809300</v>
       </c>
       <c r="I57" s="3">
-        <v>553400</v>
+        <v>29423400</v>
       </c>
       <c r="J57" s="3">
-        <v>524700</v>
+        <v>31152600</v>
       </c>
       <c r="K57" s="3">
         <v>385800</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3070500</v>
+        <v>10473700</v>
       </c>
       <c r="E58" s="3">
-        <v>3474200</v>
+        <v>7294800</v>
       </c>
       <c r="F58" s="3">
-        <v>3621900</v>
+        <v>6857600</v>
       </c>
       <c r="G58" s="3">
-        <v>2606800</v>
+        <v>7127300</v>
       </c>
       <c r="H58" s="3">
-        <v>3379900</v>
+        <v>7712600</v>
       </c>
       <c r="I58" s="3">
-        <v>3343300</v>
+        <v>6503600</v>
       </c>
       <c r="J58" s="3">
-        <v>2713600</v>
+        <v>6186000</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>5</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>684800</v>
+        <v>1237000</v>
       </c>
       <c r="E59" s="3">
-        <v>576500</v>
+        <v>1723100</v>
       </c>
       <c r="F59" s="3">
-        <v>477500</v>
+        <v>1652500</v>
       </c>
       <c r="G59" s="3">
-        <v>242900</v>
+        <v>2418600</v>
       </c>
       <c r="H59" s="3">
-        <v>408400</v>
+        <v>1168600</v>
       </c>
       <c r="I59" s="3">
-        <v>353600</v>
+        <v>1115400</v>
       </c>
       <c r="J59" s="3">
-        <v>342900</v>
+        <v>1190600</v>
       </c>
       <c r="K59" s="3">
         <v>323900</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>45587000</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>42522700</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>40785600</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>43938800</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>38818400</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>37171200</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>38662200</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>14596700</v>
+        <v>10486400</v>
       </c>
       <c r="E61" s="3">
-        <v>14158100</v>
+        <v>15430900</v>
       </c>
       <c r="F61" s="3">
-        <v>12368700</v>
+        <v>13776600</v>
       </c>
       <c r="G61" s="3">
-        <v>11280900</v>
+        <v>14701000</v>
       </c>
       <c r="H61" s="3">
-        <v>8486800</v>
+        <v>10440300</v>
       </c>
       <c r="I61" s="3">
-        <v>6824000</v>
+        <v>9095400</v>
       </c>
       <c r="J61" s="3">
-        <v>5944300</v>
+        <v>8913900</v>
       </c>
       <c r="K61" s="3">
         <v>8366700</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1038200</v>
+        <v>440500</v>
       </c>
       <c r="E62" s="3">
-        <v>1017100</v>
+        <v>399400</v>
       </c>
       <c r="F62" s="3">
-        <v>782000</v>
+        <v>1015100</v>
       </c>
       <c r="G62" s="3">
-        <v>554700</v>
+        <v>838500</v>
       </c>
       <c r="H62" s="3">
-        <v>414900</v>
+        <v>732300</v>
       </c>
       <c r="I62" s="3">
-        <v>393900</v>
+        <v>710900</v>
       </c>
       <c r="J62" s="3">
-        <v>413600</v>
+        <v>670800</v>
       </c>
       <c r="K62" s="3">
         <v>425800</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>54599700</v>
+        <v>56616300</v>
       </c>
       <c r="E66" s="3">
-        <v>54428800</v>
+        <v>58475000</v>
       </c>
       <c r="F66" s="3">
-        <v>51277800</v>
+        <v>55709900</v>
       </c>
       <c r="G66" s="3">
-        <v>45758400</v>
+        <v>59632500</v>
       </c>
       <c r="H66" s="3">
-        <v>40764700</v>
+        <v>50198300</v>
       </c>
       <c r="I66" s="3">
-        <v>35232100</v>
+        <v>47011600</v>
       </c>
       <c r="J66" s="3">
-        <v>32096000</v>
+        <v>48285400</v>
       </c>
       <c r="K66" s="3">
         <v>32370300</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>3012100</v>
+        <v>2772100</v>
       </c>
       <c r="E72" s="3">
-        <v>2741100</v>
+        <v>2248100</v>
       </c>
       <c r="F72" s="3">
-        <v>1945700</v>
+        <v>1319000</v>
       </c>
       <c r="G72" s="3">
-        <v>1487500</v>
+        <v>1867700</v>
       </c>
       <c r="H72" s="3">
-        <v>1281500</v>
+        <v>1508400</v>
       </c>
       <c r="I72" s="3">
-        <v>1013800</v>
+        <v>1286300</v>
       </c>
       <c r="J72" s="3">
-        <v>912600</v>
+        <v>1316500</v>
       </c>
       <c r="K72" s="3">
         <v>876900</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>5656300</v>
+        <v>6937200</v>
       </c>
       <c r="E76" s="3">
-        <v>5247000</v>
+        <v>6393300</v>
       </c>
       <c r="F76" s="3">
-        <v>4560900</v>
+        <v>5039300</v>
       </c>
       <c r="G76" s="3">
-        <v>4024400</v>
+        <v>5244600</v>
       </c>
       <c r="H76" s="3">
-        <v>3810500</v>
+        <v>4692300</v>
       </c>
       <c r="I76" s="3">
-        <v>3568500</v>
+        <v>4761600</v>
       </c>
       <c r="J76" s="3">
-        <v>3354200</v>
+        <v>5046000</v>
       </c>
       <c r="K76" s="3">
         <v>3262800</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1343100</v>
+        <v>1567300</v>
       </c>
       <c r="E81" s="3">
-        <v>1522200</v>
+        <v>1701800</v>
       </c>
       <c r="F81" s="3">
-        <v>856400</v>
+        <v>1239800</v>
       </c>
       <c r="G81" s="3">
-        <v>500200</v>
+        <v>651800</v>
       </c>
       <c r="H81" s="3">
-        <v>640400</v>
+        <v>788700</v>
       </c>
       <c r="I81" s="3">
-        <v>642500</v>
+        <v>857300</v>
       </c>
       <c r="J81" s="3">
-        <v>622100</v>
+        <v>935900</v>
       </c>
       <c r="K81" s="3">
         <v>624000</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>99700</v>
+        <v>71800</v>
       </c>
       <c r="E83" s="3">
-        <v>90900</v>
+        <v>73800</v>
       </c>
       <c r="F83" s="3">
-        <v>82900</v>
+        <v>69200</v>
       </c>
       <c r="G83" s="3">
-        <v>79200</v>
+        <v>80900</v>
       </c>
       <c r="H83" s="3">
-        <v>76200</v>
+        <v>76700</v>
       </c>
       <c r="I83" s="3">
-        <v>40700</v>
+        <v>39200</v>
       </c>
       <c r="J83" s="3">
-        <v>38100</v>
+        <v>42500</v>
       </c>
       <c r="K83" s="3">
         <v>37600</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1124700</v>
+        <v>567700</v>
       </c>
       <c r="E89" s="3">
-        <v>-360300</v>
+        <v>60000</v>
       </c>
       <c r="F89" s="3">
-        <v>2623800</v>
+        <v>-702100</v>
       </c>
       <c r="G89" s="3">
-        <v>561200</v>
+        <v>-2002100</v>
       </c>
       <c r="H89" s="3">
-        <v>1334700</v>
+        <v>-914900</v>
       </c>
       <c r="I89" s="3">
-        <v>-1080600</v>
+        <v>-3240900</v>
       </c>
       <c r="J89" s="3">
-        <v>1152900</v>
+        <v>1485600</v>
       </c>
       <c r="K89" s="3">
         <v>384600</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-28900</v>
+        <v>-30500</v>
       </c>
       <c r="E91" s="3">
-        <v>-22900</v>
+        <v>-25000</v>
       </c>
       <c r="F91" s="3">
-        <v>-38400</v>
+        <v>-41800</v>
       </c>
       <c r="G91" s="3">
-        <v>-31700</v>
+        <v>-40100</v>
       </c>
       <c r="H91" s="3">
-        <v>-47000</v>
+        <v>-57900</v>
       </c>
       <c r="I91" s="3">
-        <v>-30300</v>
+        <v>-40400</v>
       </c>
       <c r="J91" s="3">
-        <v>-25100</v>
+        <v>-37700</v>
       </c>
       <c r="K91" s="3">
         <v>-31400</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-83600</v>
+        <v>-395200</v>
       </c>
       <c r="E94" s="3">
-        <v>-78400</v>
+        <v>-998000</v>
       </c>
       <c r="F94" s="3">
-        <v>-3132300</v>
+        <v>-3506200</v>
       </c>
       <c r="G94" s="3">
-        <v>226700</v>
+        <v>335800</v>
       </c>
       <c r="H94" s="3">
-        <v>-429400</v>
+        <v>-528800</v>
       </c>
       <c r="I94" s="3">
-        <v>449800</v>
+        <v>600100</v>
       </c>
       <c r="J94" s="3">
-        <v>-1273700</v>
+        <v>-1916200</v>
       </c>
       <c r="K94" s="3">
         <v>455600</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-936300</v>
+        <v>988800</v>
       </c>
       <c r="E96" s="3">
-        <v>-583000</v>
+        <v>635400</v>
       </c>
       <c r="F96" s="3">
-        <v>-237900</v>
+        <v>258500</v>
       </c>
       <c r="G96" s="3">
-        <v>-378600</v>
+        <v>493400</v>
       </c>
       <c r="H96" s="3">
-        <v>-384800</v>
+        <v>473900</v>
       </c>
       <c r="I96" s="3">
-        <v>-404000</v>
+        <v>539100</v>
       </c>
       <c r="J96" s="3">
-        <v>-369400</v>
+        <v>555700</v>
       </c>
       <c r="K96" s="3">
         <v>-414300</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1664200</v>
+        <v>-374100</v>
       </c>
       <c r="E100" s="3">
-        <v>-880400</v>
+        <v>-99100</v>
       </c>
       <c r="F100" s="3">
-        <v>1453500</v>
+        <v>5845400</v>
       </c>
       <c r="G100" s="3">
-        <v>1578500</v>
+        <v>4750200</v>
       </c>
       <c r="H100" s="3">
-        <v>866600</v>
+        <v>3625700</v>
       </c>
       <c r="I100" s="3">
-        <v>696600</v>
+        <v>2728400</v>
       </c>
       <c r="J100" s="3">
-        <v>143300</v>
+        <v>464300</v>
       </c>
       <c r="K100" s="3">
         <v>-804100</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>16900</v>
+        <v>17800</v>
       </c>
       <c r="E101" s="3">
-        <v>41100</v>
+        <v>44700</v>
       </c>
       <c r="F101" s="3">
-        <v>351000</v>
+        <v>381400</v>
       </c>
       <c r="G101" s="3">
-        <v>-37100</v>
+        <v>-48400</v>
       </c>
       <c r="H101" s="3">
-        <v>37000</v>
+        <v>45600</v>
       </c>
       <c r="I101" s="3">
-        <v>125400</v>
+        <v>167300</v>
       </c>
       <c r="J101" s="3">
-        <v>-41400</v>
+        <v>-62300</v>
       </c>
       <c r="K101" s="3">
         <v>-32600</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-606100</v>
+        <v>-183800</v>
       </c>
       <c r="E102" s="3">
-        <v>-1278100</v>
+        <v>-992300</v>
       </c>
       <c r="F102" s="3">
-        <v>1296000</v>
+        <v>2018400</v>
       </c>
       <c r="G102" s="3">
-        <v>2329300</v>
+        <v>3035500</v>
       </c>
       <c r="H102" s="3">
-        <v>1809000</v>
+        <v>2227600</v>
       </c>
       <c r="I102" s="3">
-        <v>191100</v>
+        <v>255000</v>
       </c>
       <c r="J102" s="3">
-        <v>-19000</v>
+        <v>-28600</v>
       </c>
       <c r="K102" s="3">
         <v>3500</v>

--- a/AAII_Financials/Yearly/BCH_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BCH_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
   <si>
     <t>BCH</t>
   </si>
@@ -656,144 +656,150 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3210500</v>
+        <v>2675300</v>
       </c>
       <c r="E8" s="3">
+        <v>3004000</v>
+      </c>
+      <c r="F8" s="3">
         <v>3214000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2588800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2077500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2217300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2294000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2395400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2160100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2127200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2434300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2295700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2141100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2207500</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>56600</v>
+        <v>51900</v>
       </c>
       <c r="E9" s="3">
+        <v>56700</v>
+      </c>
+      <c r="F9" s="3">
         <v>49600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>46600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>67900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>68500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>55400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>58200</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>5</v>
       </c>
@@ -809,36 +815,39 @@
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>3153900</v>
+        <v>2623400</v>
       </c>
       <c r="E10" s="3">
+        <v>2947300</v>
+      </c>
+      <c r="F10" s="3">
         <v>3164400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2542300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2009600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2148800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2238600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2337100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -854,9 +863,12 @@
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -874,8 +886,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -918,9 +931,12 @@
       <c r="P12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,36 +979,39 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>2200</v>
+        <v>1500</v>
       </c>
       <c r="E14" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F14" s="3">
         <v>200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>500</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1008,54 +1027,60 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E15" s="3">
         <v>35100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>36400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>34900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>42000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>38800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>39200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>42500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-37600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-33100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-39000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-36000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-90000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-103300</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1273600</v>
+        <v>1138300</v>
       </c>
       <c r="E17" s="3">
+        <v>1271700</v>
+      </c>
+      <c r="F17" s="3">
         <v>1171600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1023100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1239200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1208000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1221000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1281900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1130000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1101200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1249900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1203800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1120100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1133600</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1936900</v>
+        <v>1537000</v>
       </c>
       <c r="E18" s="3">
+        <v>1732300</v>
+      </c>
+      <c r="F18" s="3">
         <v>2042500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1565700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>838300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1009300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1073000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1113500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1030100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1026000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1184300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1091900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1021100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1073900</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,8 +1211,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1193,84 +1226,90 @@
       <c r="F20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3">
         <v>6600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-8600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-10500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-9800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-305500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-330800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-380900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-260800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-325000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-333700</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1971900</v>
+        <v>1565700</v>
       </c>
       <c r="E21" s="3">
+        <v>1767300</v>
+      </c>
+      <c r="F21" s="3">
         <v>2078900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1600600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>873700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1056700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1122700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1165900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>762300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>727700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>842800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>867300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>741400</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1295,8 +1334,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1313,99 +1352,108 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1934700</v>
+        <v>1535400</v>
       </c>
       <c r="E23" s="3">
+        <v>1730900</v>
+      </c>
+      <c r="F23" s="3">
         <v>2042300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1563700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>829100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1014300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1082800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1122800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>724700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>695200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>803500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>831100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>696100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>740300</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>367400</v>
+        <v>320400</v>
       </c>
       <c r="E24" s="3">
+        <v>312400</v>
+      </c>
+      <c r="F24" s="3">
         <v>340400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>323900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>177300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>225700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>225600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>186900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>100600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>69100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>94800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>115800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>81800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>96200</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1567300</v>
+        <v>1215000</v>
       </c>
       <c r="E26" s="3">
+        <v>1418500</v>
+      </c>
+      <c r="F26" s="3">
         <v>1701800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1239800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>651800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>788700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>857300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>935900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>624000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>626100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>708700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>715200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>614200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>644100</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1567300</v>
+        <v>1215000</v>
       </c>
       <c r="E27" s="3">
+        <v>1418500</v>
+      </c>
+      <c r="F27" s="3">
         <v>1701800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1239800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>651800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>788700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>857300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>935900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>624000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>626100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>708700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>715200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>614200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>644100</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1628,9 +1688,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,9 +1784,12 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1733,84 +1802,90 @@
       <c r="F32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3">
         <v>-6600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>8600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>10500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>9800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>305500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>330800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>380900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>260800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>325000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>333700</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1567300</v>
+        <v>1215000</v>
       </c>
       <c r="E33" s="3">
+        <v>1418500</v>
+      </c>
+      <c r="F33" s="3">
         <v>1701800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1239800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>651800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>788700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>857300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>935900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>624000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>626100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>708700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>715200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>614200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>644100</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1567300</v>
+        <v>1215000</v>
       </c>
       <c r="E35" s="3">
+        <v>1418500</v>
+      </c>
+      <c r="F35" s="3">
         <v>1701800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1239800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>651800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>788700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>857300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>935900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>624000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>626100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>708700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>715200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>614200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>644100</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,125 +2072,132 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2047900</v>
+      </c>
+      <c r="E41" s="3">
         <v>2611700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3711200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3116200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2652800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2538200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2554500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2620700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2636400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3676400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2940000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2906000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1273600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1844500</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>9159600</v>
+        <v>4619700</v>
       </c>
       <c r="E42" s="3">
+        <v>9159400</v>
+      </c>
+      <c r="F42" s="3">
         <v>10045300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>9406500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>14674200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>8503800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4754300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2229300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2356800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1022400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1676000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1019200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1968800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1420400</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>927800</v>
+      </c>
+      <c r="E43" s="3">
         <v>841600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>602900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>371200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>169900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>141500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>153400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>267100</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
@@ -2121,36 +2213,39 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>29000</v>
+        <v>33700</v>
       </c>
       <c r="E44" s="3">
+        <v>26100</v>
+      </c>
+      <c r="F44" s="3">
         <v>16200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>18100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>9000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>17300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>25600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>22800</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
       <c r="L44" s="3">
         <v>0</v>
       </c>
@@ -2166,9 +2261,12 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2178,24 +2276,24 @@
       <c r="E45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3">
         <v>4600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>347400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>737100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>509400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>311600</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -2211,36 +2309,39 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>13767200</v>
+        <v>9090900</v>
       </c>
       <c r="E46" s="3">
+        <v>13764100</v>
+      </c>
+      <c r="F46" s="3">
         <v>15250900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>15130900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>19665200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>13405200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9127100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6584600</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2256,144 +2357,156 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3128800</v>
+      </c>
+      <c r="E47" s="3">
         <v>6039200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>5806000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4633000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>590800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>515700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1751400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3983400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>36800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>31500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>30100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>18700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>14900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>19400</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>287800</v>
+      </c>
+      <c r="E48" s="3">
         <v>354200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>359100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>378500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>474000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>493300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>311100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>351400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>264100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>258400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>836300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>278100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>284000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>330700</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>194600</v>
+        <v>159600</v>
       </c>
       <c r="E49" s="3">
+        <v>156500</v>
+      </c>
+      <c r="F49" s="3">
         <v>164800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>85100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>85400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>77500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>75000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>63400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>33200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>29900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>59700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>93900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>96800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>119100</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>196400</v>
+      </c>
+      <c r="E52" s="3">
         <v>220500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>153000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>163100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>279800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>282400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>188100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>822200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>318300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>286700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>241400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>73300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>71400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>88200</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>63553600</v>
+        <v>52424700</v>
       </c>
       <c r="E54" s="3">
+        <v>63638500</v>
+      </c>
+      <c r="F54" s="3">
         <v>64868300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>60749200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>64877000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>54890600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>51773200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>53331500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>35633100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>35048100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>32898500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>33635800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>29693700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>31981300</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,170 +2784,180 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>33700900</v>
+        <v>28976000</v>
       </c>
       <c r="E57" s="3">
+        <v>33111900</v>
+      </c>
+      <c r="F57" s="3">
         <v>33347900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>32136200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>34257400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>29809300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>29423400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>31152600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>385800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>406900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>259800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>197600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>93000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>228500</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>10473700</v>
+        <v>3840400</v>
       </c>
       <c r="E58" s="3">
+        <v>9285300</v>
+      </c>
+      <c r="F58" s="3">
         <v>7294800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6857600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7127300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7712600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6503600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6186000</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M58" s="3">
+      <c r="M58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N58" s="3">
         <v>1366100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1272200</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1237000</v>
+        <v>1365000</v>
       </c>
       <c r="E59" s="3">
+        <v>1706300</v>
+      </c>
+      <c r="F59" s="3">
         <v>1723100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1652500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2418600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1168600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1115400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1190600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>323900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>32800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>125000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>97600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>29700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4500</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>45587000</v>
+        <v>34329700</v>
       </c>
       <c r="E60" s="3">
+        <v>44278900</v>
+      </c>
+      <c r="F60" s="3">
         <v>42522700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>40785600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>43938800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>38818400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>37171200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>38662200</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -2834,99 +2973,108 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>10486400</v>
+        <v>11330100</v>
       </c>
       <c r="E61" s="3">
+        <v>12067600</v>
+      </c>
+      <c r="F61" s="3">
         <v>15430900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>13776600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>14701000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10440300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9095400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8913900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8366700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8741500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7548500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6299100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6304100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6900100</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>440500</v>
+        <v>1016900</v>
       </c>
       <c r="E62" s="3">
+        <v>1215800</v>
+      </c>
+      <c r="F62" s="3">
         <v>399400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1015100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>838500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>732300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>710900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>670800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>425800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>752600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>757700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>201000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>82600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>89100</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>56616300</v>
+        <v>46766100</v>
       </c>
       <c r="E66" s="3">
+        <v>57664800</v>
+      </c>
+      <c r="F66" s="3">
         <v>58475000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>55709900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>59632500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>50198300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>47011600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>48285400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>32370300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>31979200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>29881700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>30153100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>26678700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>28981500</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2772100</v>
+        <v>2504700</v>
       </c>
       <c r="E72" s="3">
+        <v>2375700</v>
+      </c>
+      <c r="F72" s="3">
         <v>2248100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1319000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1867700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1508400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1286300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1316500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>876900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>718100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>649900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1048700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1075700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1077500</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>6937200</v>
+        <v>5658500</v>
       </c>
       <c r="E76" s="3">
+        <v>5973800</v>
+      </c>
+      <c r="F76" s="3">
         <v>6393300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5039300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5244600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4692300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4761600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5046000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3262800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3068900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3016800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3482700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3015000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2999800</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1567300</v>
+        <v>1215000</v>
       </c>
       <c r="E81" s="3">
+        <v>1418500</v>
+      </c>
+      <c r="F81" s="3">
         <v>1701800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1239800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>651800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>788700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>857300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>935900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>624000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>626100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>708700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>715200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>614200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>644100</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>58700</v>
+      </c>
+      <c r="E83" s="3">
         <v>71800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>73800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>69200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>80900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>76700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>39200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>42500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>37600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>33100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>39000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>36000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>45000</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>567700</v>
+        <v>399100</v>
       </c>
       <c r="E89" s="3">
+        <v>-212900</v>
+      </c>
+      <c r="F89" s="3">
         <v>60000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-702100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2002100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-914900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3240900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1485600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>384600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1594600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-273200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-181800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-532500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-668700</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-17300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-30500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-25000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-41800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-40100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-57900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-40400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-37700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-31400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-35300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-37500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-15900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-23000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-32400</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-395200</v>
+        <v>-58700</v>
       </c>
       <c r="E94" s="3">
+        <v>-88300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-998000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3506200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>335800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-528800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>600100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1916200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>455600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>448100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>58600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-532000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>246200</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,53 +4453,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>821100</v>
+      </c>
+      <c r="E96" s="3">
         <v>988800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>635400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>258500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>493400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>473900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>539100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>555700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-414300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-411500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-438100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-446500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-379900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-410400</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-374100</v>
+        <v>-1567400</v>
       </c>
       <c r="E100" s="3">
+        <v>-356800</v>
+      </c>
+      <c r="F100" s="3">
         <v>-99100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>5845400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>4750200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3625700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2728400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>464300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-804100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1359500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>449300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1002100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>61600</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>165800</v>
+      </c>
+      <c r="E101" s="3">
         <v>17800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>44700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>381400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-48400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>45600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>167300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-62300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-32600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>87500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>55000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>78600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-40600</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-183800</v>
+        <v>-1061200</v>
       </c>
       <c r="E102" s="3">
+        <v>-640200</v>
+      </c>
+      <c r="F102" s="3">
         <v>-992300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2018400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3035500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2227600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>255000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-28600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>300500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>289700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>366900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-265300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>190700</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/BCH_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BCH_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
   <si>
     <t>BCH</t>
   </si>
@@ -2130,7 +2130,7 @@
         <v>4619700</v>
       </c>
       <c r="E42" s="3">
-        <v>9159400</v>
+        <v>8879300</v>
       </c>
       <c r="F42" s="3">
         <v>10045300</v>
@@ -2273,8 +2273,8 @@
       <c r="D45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>5</v>
+      <c r="E45" s="3">
+        <v>280200</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>5</v>

--- a/AAII_Financials/Yearly/BCH_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BCH_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>BCH</t>
   </si>
@@ -656,153 +656,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2935400</v>
+      </c>
+      <c r="E8" s="3">
         <v>2675300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3004000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3214000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2588800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2077500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2217300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2294000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2395400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2160100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2127200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2434300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2295700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2141100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2207500</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>58100</v>
+      </c>
+      <c r="E9" s="3">
         <v>51900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>56700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>49600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>46600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>67900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>68500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>55400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>58200</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>5</v>
       </c>
@@ -818,39 +824,42 @@
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2877300</v>
+      </c>
+      <c r="E10" s="3">
         <v>2623400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2947300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3164400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2542300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2009600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2148800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2238600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2337100</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -866,9 +875,12 @@
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -887,8 +899,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -934,9 +947,12 @@
       <c r="Q12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,39 +998,42 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E14" s="3">
         <v>1500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>500</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1030,57 +1049,63 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E15" s="3">
         <v>28700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>35100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>36400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>34900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>42000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>38800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>39200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>42500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-37600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-33100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-39000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-36000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-90000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-103300</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1254200</v>
+      </c>
+      <c r="E17" s="3">
         <v>1138300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1271700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1171600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1023100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1239200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1208000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1221000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1281900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1130000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1101200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1249900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1203800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1120100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1133600</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1681200</v>
+      </c>
+      <c r="E18" s="3">
         <v>1537000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1732300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2042500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1565700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>838300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1009300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1073000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1113500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1030100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1026000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1184300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1091900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1021100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1073900</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,8 +1244,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1229,87 +1262,93 @@
       <c r="G20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3">
         <v>6600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-8600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-10500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-9800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-305500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-330800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-380900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-260800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-325000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-333700</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1707800</v>
+      </c>
+      <c r="E21" s="3">
         <v>1565700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1767300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2078900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1600600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>873700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1056700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1122700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1165900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>762300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>727700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>842800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>867300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>741400</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1337,8 +1376,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1355,105 +1394,114 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1679900</v>
+      </c>
+      <c r="E23" s="3">
         <v>1535400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1730900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2042300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1563700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>829100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1014300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1082800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1122800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>724700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>695200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>803500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>831100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>696100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>740300</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>356300</v>
+      </c>
+      <c r="E24" s="3">
         <v>320400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>312400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>340400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>323900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>177300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>225700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>225600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>186900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>69100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>94800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>115800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>81800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>96200</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1323600</v>
+      </c>
+      <c r="E26" s="3">
         <v>1215000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1418500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1701800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1239800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>651800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>788700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>857300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>935900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>624000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>626100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>708700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>715200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>614200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>644100</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1323600</v>
+      </c>
+      <c r="E27" s="3">
         <v>1215000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1418500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1701800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1239800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>651800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>788700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>857300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>935900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>624000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>626100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>708700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>715200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>614200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>644100</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1691,9 +1751,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,9 +1853,12 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1805,87 +1874,93 @@
       <c r="G32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3">
         <v>-6600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>8600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>10500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>9800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>305500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>330800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>380900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>260800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>325000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>333700</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1323600</v>
+      </c>
+      <c r="E33" s="3">
         <v>1215000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1418500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1701800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1239800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>651800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>788700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>857300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>935900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>624000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>626100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>708700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>715200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>614200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>644100</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1323600</v>
+      </c>
+      <c r="E35" s="3">
         <v>1215000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1418500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1701800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1239800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>651800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>788700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>857300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>935900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>624000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>626100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>708700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>715200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>614200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>644100</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,134 +2158,141 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1840500</v>
+      </c>
+      <c r="E41" s="3">
         <v>2047900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2611700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3711200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3116200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2652800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2538200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2554500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2620700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2636400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3676400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2940000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2906000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1273600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1844500</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6132300</v>
+      </c>
+      <c r="E42" s="3">
         <v>4619700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>8879300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>10045300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>9406500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>14674200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>8503800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4754300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2229300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2356800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1022400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1676000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1019200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1968800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1420400</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1129400</v>
+      </c>
+      <c r="E43" s="3">
         <v>927800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>841600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>602900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>371200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>169900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>141500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>153400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>267100</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
@@ -2216,39 +2308,42 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E44" s="3">
         <v>33700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>26100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>16200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>18100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>9000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>17300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>25600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>22800</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
@@ -2264,39 +2359,42 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3">
         <v>280200</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3">
         <v>4600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>347400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>737100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>509400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>311600</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -2312,39 +2410,42 @@
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11197800</v>
+      </c>
+      <c r="E46" s="3">
         <v>9090900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13764100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>15250900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>15130900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>19665200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>13405200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9127100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6584600</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2360,153 +2461,165 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4548300</v>
+      </c>
+      <c r="E47" s="3">
         <v>3128800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6039200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>5806000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4633000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>590800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>515700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1751400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3983400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>36800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>31500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>30100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>18700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>14900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>19400</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>287200</v>
+      </c>
+      <c r="E48" s="3">
         <v>287800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>354200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>359100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>378500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>474000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>493300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>311100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>351400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>264100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>258400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>836300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>278100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>284000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>330700</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>193800</v>
+      </c>
+      <c r="E49" s="3">
         <v>159600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>156500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>164800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>85100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>85400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>77500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>75000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>63400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>33200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>29900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>59700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>93900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>96800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>119100</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>184300</v>
+      </c>
+      <c r="E52" s="3">
         <v>196400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>220500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>153000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>163100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>279800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>282400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>188100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>822200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>318300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>286700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>241400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>73300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>71400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>88200</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>60060700</v>
+      </c>
+      <c r="E54" s="3">
         <v>52424700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>63638500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>64868300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>60749200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>64877000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>54890600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>51773200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>53331500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>35633100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>35048100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>32898500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>33635800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>29693700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>31981300</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,182 +2914,192 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>28976000</v>
+        <v>32090200</v>
       </c>
       <c r="E57" s="3">
+        <v>29040100</v>
+      </c>
+      <c r="F57" s="3">
         <v>33111900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>33347900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>32136200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>34257400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>29809300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>29423400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>31152600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>385800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>406900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>259800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>197600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>93000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>228500</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5302200</v>
+      </c>
+      <c r="E58" s="3">
         <v>3840400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>9285300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7294800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6857600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7127300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7712600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6503600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6186000</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N58" s="3">
+      <c r="N58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O58" s="3">
         <v>1366100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1272200</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1975000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1365000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1706300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1723100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1652500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2418600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1168600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1115400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1190600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>323900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>32800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>125000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>97600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>29700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4500</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>34329700</v>
+        <v>39518500</v>
       </c>
       <c r="E60" s="3">
+        <v>34393900</v>
+      </c>
+      <c r="F60" s="3">
         <v>44278900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>42522700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>40785600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>43938800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>38818400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>37171200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>38662200</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -2976,105 +3115,114 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>11330100</v>
+        <v>12695500</v>
       </c>
       <c r="E61" s="3">
+        <v>11265900</v>
+      </c>
+      <c r="F61" s="3">
         <v>12067600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>15430900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>13776600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>14701000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>10440300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9095400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8913900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8366700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8741500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7548500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6299100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6304100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6900100</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1313500</v>
+      </c>
+      <c r="E62" s="3">
         <v>1016900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1215800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>399400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1015100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>838500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>732300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>710900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>670800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>425800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>752600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>757700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>201000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>82600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>89100</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>53622300</v>
+      </c>
+      <c r="E66" s="3">
         <v>46766100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>57664800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>58475000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>55709900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>59632500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>50198300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>47011600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>48285400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>32370300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>31979200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>29881700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>30153100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>26678700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>28981500</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2972000</v>
+      </c>
+      <c r="E72" s="3">
         <v>2504700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2375700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2248100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1319000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1867700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1508400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1286300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1316500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>876900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>718100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>649900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1048700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1075700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1077500</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6438400</v>
+      </c>
+      <c r="E76" s="3">
         <v>5658500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5973800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6393300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5039300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5244600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4692300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4761600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5046000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3262800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3068900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3016800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3482700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3015000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2999800</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1323600</v>
+      </c>
+      <c r="E81" s="3">
         <v>1215000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1418500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1701800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1239800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>651800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>788700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>857300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>935900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>624000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>626100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>708700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>715200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>614200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>644100</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>59600</v>
+      </c>
+      <c r="E83" s="3">
         <v>58700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>71800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>73800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>69200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>80900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>76700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>39200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>42500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>37600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>33100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>39000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>36000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>45000</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1385900</v>
+      </c>
+      <c r="E89" s="3">
         <v>399100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-212900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>60000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-702100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2002100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-914900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3240900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1485600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>384600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1594600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-273200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-181800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-532500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-668700</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-20800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-17300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-30500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-25000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-41800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-40100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-57900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-40400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-37700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-31400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-35300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-37500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-15900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-23000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-32400</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-71500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-58700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-88300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-998000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3506200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>335800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-528800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>600100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1916200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>455600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>448100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>58600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-532000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>246200</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,56 +4686,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1105000</v>
+      </c>
+      <c r="E96" s="3">
         <v>821100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>988800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>635400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>258500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>493400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>473900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>539100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>555700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-414300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-411500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-438100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-446500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-379900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-410400</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-303400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1567400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-356800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-99100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>5845400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>4750200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3625700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2728400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>464300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-804100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1359500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>449300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1002100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>61600</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-86700</v>
+      </c>
+      <c r="E101" s="3">
         <v>165800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>17800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>44700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>381400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-48400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>45600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>167300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-62300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-32600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>87500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>55000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>78600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-40600</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>924300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1061200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-640200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-992300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2018400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3035500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2227600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>255000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-28600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>300500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>289700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>366900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-265300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>190700</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
